--- a/dev_docs/Tetra数值表_26_5_11.xlsx
+++ b/dev_docs/Tetra数值表_26_5_11.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tony\AppData\Roaming\PrismLauncher\instances\SenDimsBanForges\minecraft\dev_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1900DAE3-DBF9-47DD-A964-F7C66F6FD799}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8F64AD1-3B13-4DCE-92CE-495D419D0C11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="429">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="686" uniqueCount="441">
   <si>
     <t>刀刃</t>
   </si>
@@ -112,9 +112,6 @@
     <t>盔甲韧性</t>
   </si>
   <si>
-    <t>癫火抵抗+%</t>
-  </si>
-  <si>
     <t>软的只能做刀镡</t>
   </si>
   <si>
@@ -566,9 +563,6 @@
   </si>
   <si>
     <t>火焰伤害+1</t>
-  </si>
-  <si>
-    <t>癫火抵抗+0.05</t>
   </si>
   <si>
     <t>1.2.9</t>
@@ -961,23 +955,6 @@
   </si>
   <si>
     <t>暴击率+0.06</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>癫火抵抗+0.1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>5</t>
-    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1155,10 +1132,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>癫火抵抗+0.05</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>火焰伤害+4</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1797,10 +1770,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>魔力共振</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>魔力修复</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1900,12 +1869,118 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>暴击率+0.1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t>护甲穿透+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>闪耀蜜蜂结晶</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>红石蜜蜂网</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>古蜡砖</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>蜂王浆</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>多面酒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>魔法抗性+3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>盔甲撕裂+2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>%</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>魔力共振2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>魔法穿透+2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>击退抗性+0.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>05</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>癫火抗性+%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>发狂抵抗</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>癫火抗性+0.05</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>癫火抗性+0.15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>发狂抵抗+20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>暴击率+0.07</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>经验获取+0.</t>
     </r>
     <r>
       <rPr>
@@ -2461,7 +2536,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X162"/>
+  <dimension ref="A1:X165"/>
   <sheetFormatPr defaultColWidth="16.625" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="3" width="8.625" style="3" customWidth="1"/>
@@ -2489,10 +2564,10 @@
         <v>4</v>
       </c>
       <c r="J1" s="24" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="K1" s="24" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="M1" s="3" t="s">
         <v>5</v>
@@ -2513,10 +2588,10 @@
         <v>10</v>
       </c>
       <c r="T1" s="24" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="U1" s="30" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="V1" s="30"/>
     </row>
@@ -2570,10 +2645,10 @@
         <v>14</v>
       </c>
       <c r="T2" s="27" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="U2" s="30" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="V2" s="30"/>
       <c r="W2" s="30"/>
@@ -2626,7 +2701,7 @@
         <v>20</v>
       </c>
       <c r="U3" s="30" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="V3" s="31"/>
       <c r="W3" s="31"/>
@@ -2692,7 +2767,7 @@
         <v>26</v>
       </c>
       <c r="Q5" s="24" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="R5" s="3" t="s">
         <v>27</v>
@@ -2759,15 +2834,18 @@
         <v>0</v>
       </c>
       <c r="P7" s="24" t="s">
-        <v>421</v>
-      </c>
-      <c r="Q7" s="3" t="s">
-        <v>29</v>
+        <v>416</v>
+      </c>
+      <c r="Q7" s="24" t="s">
+        <v>433</v>
+      </c>
+      <c r="R7" s="24" t="s">
+        <v>434</v>
       </c>
     </row>
     <row r="8" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F8" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P8" s="3" t="s">
         <v>14</v>
@@ -2775,10 +2853,13 @@
       <c r="Q8" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="R8" s="24" t="s">
+        <v>435</v>
+      </c>
     </row>
     <row r="9" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F9" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>12</v>
@@ -2790,36 +2871,36 @@
         <v>22</v>
       </c>
       <c r="U9" s="3" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
     </row>
     <row r="10" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="C10" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="D10" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="E10" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="F10" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="G10" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="G10" s="5" t="s">
+      <c r="H10" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="H10" s="6" t="s">
+      <c r="I10" s="7" t="s">
         <v>39</v>
-      </c>
-      <c r="I10" s="7" t="s">
-        <v>40</v>
       </c>
       <c r="J10" s="14" t="s">
         <v>11</v>
@@ -2828,7 +2909,7 @@
         <v>25</v>
       </c>
       <c r="L10" s="15" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="M10" s="16" t="s">
         <v>21</v>
@@ -2837,25 +2918,25 @@
         <v>28</v>
       </c>
       <c r="O10" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="P10" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="P10" s="8" t="s">
+      <c r="Q10" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="Q10" s="4" t="s">
+      <c r="R10" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="R10" s="4" t="s">
+      <c r="S10" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="S10" s="4" t="s">
-        <v>46</v>
-      </c>
       <c r="T10" s="28" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="U10" s="3" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
     </row>
     <row r="11" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
@@ -2866,16 +2947,16 @@
         <v>7</v>
       </c>
       <c r="C11" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="D11" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="D11" s="12" t="s">
+      <c r="E11" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="E11" s="12" t="s">
+      <c r="F11" s="12" t="s">
         <v>49</v>
-      </c>
-      <c r="F11" s="12" t="s">
-        <v>50</v>
       </c>
       <c r="G11" s="12">
         <v>1.3</v>
@@ -2913,23 +2994,23 @@
         <v>1</v>
       </c>
       <c r="Q11" s="9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="R11" s="9"/>
       <c r="S11" s="9"/>
     </row>
     <row r="12" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C12" s="12" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D12" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="E12" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="E12" s="12" t="s">
+      <c r="F12" s="12" t="s">
         <v>53</v>
-      </c>
-      <c r="F12" s="12" t="s">
-        <v>54</v>
       </c>
       <c r="G12" s="12">
         <v>1.4</v>
@@ -2972,16 +3053,16 @@
     </row>
     <row r="13" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C13" s="12" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D13" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="E13" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="E13" s="12" t="s">
-        <v>56</v>
-      </c>
       <c r="F13" s="12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G13" s="12">
         <v>1.4</v>
@@ -3019,7 +3100,7 @@
         <v>2</v>
       </c>
       <c r="Q13" s="9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="R13" s="9"/>
       <c r="S13" s="9"/>
@@ -3032,16 +3113,16 @@
         <v>8</v>
       </c>
       <c r="C14" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D14" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="E14" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="E14" s="5" t="s">
-        <v>60</v>
-      </c>
       <c r="F14" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G14" s="5">
         <v>1.4</v>
@@ -3079,23 +3160,23 @@
         <v>2</v>
       </c>
       <c r="Q14" s="9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="R14" s="9"/>
       <c r="S14" s="9"/>
     </row>
     <row r="15" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C15" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D15" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="E15" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="E15" s="5" t="s">
-        <v>62</v>
-      </c>
       <c r="F15" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G15" s="5">
         <v>1.8</v>
@@ -3133,7 +3214,7 @@
         <v>2</v>
       </c>
       <c r="Q15" s="9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="R15" s="9"/>
       <c r="S15" s="9"/>
@@ -3146,16 +3227,16 @@
         <v>9</v>
       </c>
       <c r="C16" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="D16" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="D16" s="12" t="s">
+      <c r="E16" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="E16" s="12" t="s">
-        <v>66</v>
-      </c>
       <c r="F16" s="12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G16" s="12">
         <v>2</v>
@@ -3193,23 +3274,23 @@
         <v>3</v>
       </c>
       <c r="Q16" s="9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="R16" s="9"/>
       <c r="S16" s="9"/>
     </row>
     <row r="17" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C17" s="12" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D17" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="E17" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="E17" s="12" t="s">
-        <v>69</v>
-      </c>
       <c r="F17" s="12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G17" s="12">
         <v>2.2999999999999998</v>
@@ -3247,7 +3328,7 @@
         <v>3</v>
       </c>
       <c r="Q17" s="9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="R17" s="9"/>
       <c r="S17" s="9"/>
@@ -3260,16 +3341,16 @@
         <v>10</v>
       </c>
       <c r="C18" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="D18" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="D18" s="5" t="s">
+      <c r="E18" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="E18" s="5" t="s">
-        <v>72</v>
-      </c>
       <c r="F18" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G18" s="5">
         <v>2.6</v>
@@ -3307,7 +3388,7 @@
         <v>3</v>
       </c>
       <c r="Q18" s="9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="R18" s="9"/>
       <c r="S18" s="9"/>
@@ -3320,14 +3401,14 @@
         <v>6</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D19" s="12"/>
       <c r="E19" s="12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F19" s="12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G19" s="18">
         <v>0.8</v>
@@ -3365,21 +3446,21 @@
         <v>3</v>
       </c>
       <c r="Q19" s="9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="R19" s="9"/>
       <c r="S19" s="9"/>
     </row>
     <row r="20" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C20" s="12" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D20" s="12"/>
       <c r="E20" s="12" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F20" s="12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G20" s="18">
         <v>1.1000000000000001</v>
@@ -3417,7 +3498,7 @@
         <v>3</v>
       </c>
       <c r="Q20" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="R20" s="9"/>
       <c r="S20" s="9"/>
@@ -3430,14 +3511,14 @@
         <v>7</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G21" s="19">
         <v>1.6</v>
@@ -3475,7 +3556,7 @@
         <v>2</v>
       </c>
       <c r="Q21" s="23" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="R21" s="9"/>
       <c r="S21" s="9"/>
@@ -3483,14 +3564,14 @@
     </row>
     <row r="22" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C22" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D22" s="5"/>
       <c r="E22" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G22" s="19">
         <v>1.3</v>
@@ -3528,21 +3609,21 @@
         <v>2</v>
       </c>
       <c r="Q22" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="R22" s="9"/>
       <c r="S22" s="9"/>
     </row>
     <row r="23" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C23" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D23" s="5"/>
       <c r="E23" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G23" s="19">
         <v>1.2</v>
@@ -3580,7 +3661,7 @@
         <v>2</v>
       </c>
       <c r="Q23" s="9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="R23" s="9"/>
       <c r="S23" s="9"/>
@@ -3593,14 +3674,14 @@
         <v>8</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D24" s="12"/>
       <c r="E24" s="12" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F24" s="12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G24" s="20">
         <v>1.5</v>
@@ -3638,23 +3719,23 @@
         <v>2</v>
       </c>
       <c r="Q24" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="R24" s="9" t="s">
         <v>87</v>
-      </c>
-      <c r="R24" s="9" t="s">
-        <v>88</v>
       </c>
       <c r="S24" s="9"/>
     </row>
     <row r="25" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C25" s="12" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D25" s="12"/>
       <c r="E25" s="12" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F25" s="12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G25" s="18">
         <v>1.6</v>
@@ -3692,7 +3773,7 @@
         <v>2</v>
       </c>
       <c r="Q25" s="9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="R25" s="23"/>
       <c r="S25" s="9"/>
@@ -3700,14 +3781,14 @@
     </row>
     <row r="26" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C26" s="12" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D26" s="12"/>
       <c r="E26" s="12" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F26" s="12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G26" s="18">
         <v>1.8</v>
@@ -3745,10 +3826,10 @@
         <v>3</v>
       </c>
       <c r="Q26" s="9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="R26" s="23" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="S26" s="9"/>
       <c r="U26" s="24"/>
@@ -3761,14 +3842,14 @@
         <v>9</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D27" s="5"/>
       <c r="E27" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G27" s="19">
         <v>2</v>
@@ -3806,21 +3887,21 @@
         <v>3</v>
       </c>
       <c r="Q27" s="9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="R27" s="9"/>
       <c r="S27" s="9"/>
     </row>
     <row r="28" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C28" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D28" s="5"/>
       <c r="E28" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G28" s="19">
         <v>2.1</v>
@@ -3858,21 +3939,21 @@
         <v>4</v>
       </c>
       <c r="Q28" s="9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="R28" s="9"/>
       <c r="S28" s="9"/>
     </row>
     <row r="29" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C29" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D29" s="5"/>
       <c r="E29" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G29" s="19">
         <v>2.2999999999999998</v>
@@ -3910,7 +3991,7 @@
         <v>4</v>
       </c>
       <c r="Q29" s="9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="R29" s="9"/>
       <c r="S29" s="9"/>
@@ -3923,14 +4004,14 @@
         <v>10</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D30" s="12"/>
       <c r="E30" s="12" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F30" s="12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G30" s="18">
         <v>2.5</v>
@@ -3968,24 +4049,24 @@
         <v>4</v>
       </c>
       <c r="Q30" s="9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="R30" s="23" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="S30" s="9"/>
       <c r="U30" s="24"/>
     </row>
     <row r="31" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C31" s="12" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D31" s="12"/>
       <c r="E31" s="12" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F31" s="12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G31" s="18">
         <v>2.6</v>
@@ -4023,10 +4104,10 @@
         <v>4</v>
       </c>
       <c r="Q31" s="9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="R31" s="23" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="S31" s="9"/>
       <c r="U31" s="24"/>
@@ -4039,16 +4120,16 @@
         <v>12</v>
       </c>
       <c r="C32" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="D32" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="D32" s="5" t="s">
+      <c r="E32" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="E32" s="5" t="s">
-        <v>104</v>
-      </c>
       <c r="F32" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G32" s="19">
         <v>2.2999999999999998</v>
@@ -4086,23 +4167,23 @@
         <v>4</v>
       </c>
       <c r="Q32" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="R32" s="9"/>
       <c r="S32" s="9"/>
     </row>
     <row r="33" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C33" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D33" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="E33" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="E33" s="5" t="s">
-        <v>107</v>
-      </c>
       <c r="F33" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G33" s="19">
         <v>2.2000000000000002</v>
@@ -4140,23 +4221,23 @@
         <v>4</v>
       </c>
       <c r="Q33" s="9" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="R33" s="9"/>
       <c r="S33" s="9"/>
     </row>
     <row r="34" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C34" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D34" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="E34" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="E34" s="5" t="s">
-        <v>110</v>
-      </c>
       <c r="F34" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G34" s="19">
         <v>2.2000000000000002</v>
@@ -4194,7 +4275,7 @@
         <v>5</v>
       </c>
       <c r="Q34" s="23" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="R34" s="9"/>
       <c r="S34" s="9"/>
@@ -4208,16 +4289,16 @@
         <v>12.5</v>
       </c>
       <c r="C35" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="D35" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="D35" s="12" t="s">
+      <c r="E35" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="E35" s="12" t="s">
-        <v>113</v>
-      </c>
       <c r="F35" s="12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G35" s="18">
         <v>2.2999999999999998</v>
@@ -4255,26 +4336,26 @@
         <v>5</v>
       </c>
       <c r="Q35" s="9" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="R35" s="23" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="S35" s="9"/>
       <c r="U35" s="24"/>
     </row>
     <row r="36" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C36" s="12" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D36" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="E36" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="E36" s="12" t="s">
-        <v>116</v>
-      </c>
       <c r="F36" s="12" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G36" s="18">
         <v>2.4</v>
@@ -4312,23 +4393,23 @@
         <v>4</v>
       </c>
       <c r="Q36" s="9" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="R36" s="9"/>
       <c r="S36" s="9"/>
     </row>
     <row r="37" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C37" s="12" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D37" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="E37" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="E37" s="12" t="s">
-        <v>119</v>
-      </c>
       <c r="F37" s="12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G37" s="18">
         <v>2.5</v>
@@ -4366,7 +4447,7 @@
         <v>4</v>
       </c>
       <c r="Q37" s="9" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="R37" s="9"/>
       <c r="S37" s="9"/>
@@ -4379,16 +4460,16 @@
         <v>13</v>
       </c>
       <c r="C38" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="D38" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="D38" s="5" t="s">
+      <c r="E38" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="E38" s="5" t="s">
-        <v>123</v>
-      </c>
       <c r="F38" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G38" s="19">
         <v>2.8</v>
@@ -4426,23 +4507,23 @@
         <v>4</v>
       </c>
       <c r="Q38" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="R38" s="9"/>
       <c r="S38" s="9"/>
     </row>
     <row r="39" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C39" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D39" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="E39" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="E39" s="5" t="s">
-        <v>125</v>
-      </c>
       <c r="F39" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G39" s="19">
         <v>2.8</v>
@@ -4480,23 +4561,23 @@
         <v>4</v>
       </c>
       <c r="Q39" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="R39" s="9"/>
       <c r="S39" s="9"/>
     </row>
     <row r="40" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C40" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D40" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="E40" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="E40" s="5" t="s">
-        <v>128</v>
-      </c>
       <c r="F40" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G40" s="19">
         <v>3</v>
@@ -4534,7 +4615,7 @@
         <v>4</v>
       </c>
       <c r="Q40" s="23" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="R40" s="9"/>
       <c r="S40" s="9"/>
@@ -4548,16 +4629,16 @@
         <v>13.5</v>
       </c>
       <c r="C41" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="D41" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="D41" s="12" t="s">
+      <c r="E41" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="E41" s="12" t="s">
-        <v>131</v>
-      </c>
       <c r="F41" s="12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G41" s="18">
         <v>3</v>
@@ -4595,23 +4676,23 @@
         <v>3</v>
       </c>
       <c r="Q41" s="9" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="R41" s="9"/>
       <c r="S41" s="9"/>
     </row>
     <row r="42" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C42" s="12" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D42" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="E42" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="E42" s="12" t="s">
-        <v>134</v>
-      </c>
       <c r="F42" s="12" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G42" s="18">
         <v>3.2</v>
@@ -4649,10 +4730,10 @@
         <v>6</v>
       </c>
       <c r="Q42" s="9" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="R42" s="23" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="S42" s="9"/>
       <c r="U42" s="24"/>
@@ -4665,16 +4746,16 @@
         <v>14</v>
       </c>
       <c r="C43" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="D43" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="D43" s="5" t="s">
+      <c r="E43" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="E43" s="5" t="s">
-        <v>137</v>
-      </c>
       <c r="F43" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G43" s="19">
         <v>3.3</v>
@@ -4712,23 +4793,23 @@
         <v>5</v>
       </c>
       <c r="Q43" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="R43" s="9"/>
       <c r="S43" s="9"/>
     </row>
     <row r="44" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C44" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D44" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="E44" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="E44" s="5" t="s">
-        <v>139</v>
-      </c>
       <c r="F44" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G44" s="19">
         <v>3.4</v>
@@ -4766,7 +4847,7 @@
         <v>4</v>
       </c>
       <c r="Q44" s="23" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="R44" s="9"/>
       <c r="S44" s="9"/>
@@ -4774,16 +4855,16 @@
     </row>
     <row r="45" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C45" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D45" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="E45" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="E45" s="5" t="s">
-        <v>141</v>
-      </c>
       <c r="F45" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G45" s="19">
         <v>3.6</v>
@@ -4821,23 +4902,23 @@
         <v>4</v>
       </c>
       <c r="Q45" s="9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="R45" s="9"/>
       <c r="S45" s="9"/>
     </row>
     <row r="46" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C46" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D46" s="22" t="s">
+        <v>141</v>
+      </c>
+      <c r="E46" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="E46" s="5" t="s">
-        <v>143</v>
-      </c>
       <c r="F46" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G46" s="19">
         <v>2</v>
@@ -4875,7 +4956,7 @@
         <v>2</v>
       </c>
       <c r="Q46" s="9" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="R46" s="9"/>
       <c r="S46" s="9"/>
@@ -4888,16 +4969,16 @@
         <v>15</v>
       </c>
       <c r="C47" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="D47" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="D47" s="12" t="s">
+      <c r="E47" s="12" t="s">
         <v>146</v>
       </c>
-      <c r="E47" s="12" t="s">
-        <v>147</v>
-      </c>
       <c r="F47" s="12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G47" s="18">
         <v>3.5</v>
@@ -4935,23 +5016,23 @@
         <v>3</v>
       </c>
       <c r="Q47" s="9" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="R47" s="9"/>
       <c r="S47" s="9"/>
     </row>
     <row r="48" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C48" s="12" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D48" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="E48" s="12" t="s">
         <v>149</v>
       </c>
-      <c r="E48" s="12" t="s">
-        <v>150</v>
-      </c>
       <c r="F48" s="12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G48" s="18">
         <v>4</v>
@@ -4989,7 +5070,7 @@
         <v>4</v>
       </c>
       <c r="Q48" s="23" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="R48" s="9"/>
       <c r="S48" s="9"/>
@@ -5003,16 +5084,16 @@
         <v>16</v>
       </c>
       <c r="C49" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="D49" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="D49" s="5" t="s">
+      <c r="E49" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="E49" s="5" t="s">
-        <v>153</v>
-      </c>
       <c r="F49" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G49" s="19">
         <v>4.0999999999999996</v>
@@ -5050,25 +5131,25 @@
         <v>4</v>
       </c>
       <c r="Q49" s="9" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="R49" s="9" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="S49" s="9"/>
     </row>
     <row r="50" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C50" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D50" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="E50" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="E50" s="5" t="s">
-        <v>156</v>
-      </c>
       <c r="F50" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G50" s="19">
         <v>4.2</v>
@@ -5106,25 +5187,25 @@
         <v>5</v>
       </c>
       <c r="Q50" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="R50" s="9" t="s">
         <v>157</v>
-      </c>
-      <c r="R50" s="9" t="s">
-        <v>158</v>
       </c>
       <c r="S50" s="9"/>
     </row>
     <row r="51" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C51" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D51" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="E51" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="E51" s="5" t="s">
-        <v>160</v>
-      </c>
       <c r="F51" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G51" s="19">
         <v>4.5999999999999996</v>
@@ -5162,23 +5243,23 @@
         <v>4</v>
       </c>
       <c r="Q51" s="9" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="R51" s="9"/>
       <c r="S51" s="9"/>
     </row>
     <row r="52" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C52" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D52" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="E52" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="E52" s="5" t="s">
-        <v>163</v>
-      </c>
       <c r="F52" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G52" s="19">
         <v>4.5999999999999996</v>
@@ -5216,7 +5297,7 @@
         <v>5</v>
       </c>
       <c r="Q52" s="9" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="R52" s="9"/>
       <c r="S52" s="9"/>
@@ -5229,16 +5310,16 @@
         <v>18</v>
       </c>
       <c r="C53" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="D53" s="12" t="s">
         <v>165</v>
       </c>
-      <c r="D53" s="12" t="s">
+      <c r="E53" s="12" t="s">
         <v>166</v>
       </c>
-      <c r="E53" s="12" t="s">
-        <v>167</v>
-      </c>
       <c r="F53" s="12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G53" s="18">
         <v>4.2</v>
@@ -5276,23 +5357,23 @@
         <v>5</v>
       </c>
       <c r="Q53" s="9" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="R53" s="9"/>
       <c r="S53" s="9"/>
     </row>
     <row r="54" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C54" s="12" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D54" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="E54" s="12" t="s">
         <v>169</v>
       </c>
-      <c r="E54" s="12" t="s">
-        <v>170</v>
-      </c>
       <c r="F54" s="12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G54" s="18">
         <v>6</v>
@@ -5330,7 +5411,7 @@
         <v>5</v>
       </c>
       <c r="Q54" s="23" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="R54" s="9"/>
       <c r="S54" s="9"/>
@@ -5338,16 +5419,16 @@
     </row>
     <row r="55" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C55" s="12" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D55" s="12" t="s">
+        <v>170</v>
+      </c>
+      <c r="E55" s="12" t="s">
         <v>171</v>
       </c>
-      <c r="E55" s="12" t="s">
-        <v>172</v>
-      </c>
       <c r="F55" s="12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G55" s="18">
         <v>4.2</v>
@@ -5385,25 +5466,25 @@
         <v>5</v>
       </c>
       <c r="Q55" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="R55" s="9" t="s">
         <v>173</v>
-      </c>
-      <c r="R55" s="9" t="s">
-        <v>174</v>
       </c>
       <c r="S55" s="9"/>
     </row>
     <row r="56" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C56" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="D56" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="D56" s="5" t="s">
+      <c r="E56" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="E56" s="5" t="s">
-        <v>177</v>
-      </c>
       <c r="F56" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G56" s="19">
         <v>5.4</v>
@@ -5441,23 +5522,23 @@
         <v>4</v>
       </c>
       <c r="Q56" s="9" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="R56" s="9"/>
       <c r="S56" s="9"/>
     </row>
     <row r="57" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C57" s="5" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D57" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="E57" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="E57" s="5" t="s">
-        <v>179</v>
-      </c>
       <c r="F57" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G57" s="19">
         <v>5.4</v>
@@ -5495,10 +5576,10 @@
         <v>4</v>
       </c>
       <c r="Q57" s="9" t="s">
-        <v>180</v>
-      </c>
-      <c r="R57" s="9" t="s">
-        <v>181</v>
+        <v>179</v>
+      </c>
+      <c r="R57" s="23" t="s">
+        <v>436</v>
       </c>
       <c r="S57" s="9"/>
     </row>
@@ -5510,16 +5591,16 @@
         <v>20</v>
       </c>
       <c r="C58" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="D58" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="E58" s="12" t="s">
         <v>182</v>
       </c>
-      <c r="D58" s="12" t="s">
-        <v>183</v>
-      </c>
-      <c r="E58" s="12" t="s">
-        <v>184</v>
-      </c>
       <c r="F58" s="12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G58" s="18">
         <v>6.3</v>
@@ -5557,13 +5638,13 @@
         <v>6</v>
       </c>
       <c r="Q58" s="9" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="R58" s="9" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="S58" s="23" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="U58" s="24"/>
     </row>
@@ -5575,16 +5656,16 @@
         <v>15</v>
       </c>
       <c r="C59" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="D59" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="E59" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="D59" s="5" t="s">
-        <v>187</v>
-      </c>
-      <c r="E59" s="5" t="s">
-        <v>188</v>
-      </c>
       <c r="F59" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G59" s="5">
         <v>5.5</v>
@@ -5622,23 +5703,23 @@
         <v>2</v>
       </c>
       <c r="Q59" s="9" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="R59" s="9"/>
       <c r="S59" s="9"/>
     </row>
     <row r="60" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C60" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="D60" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="E60" s="5" t="s">
         <v>189</v>
       </c>
-      <c r="D60" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="E60" s="5" t="s">
-        <v>191</v>
-      </c>
       <c r="F60" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G60" s="5">
         <v>3</v>
@@ -5676,10 +5757,10 @@
         <v>1</v>
       </c>
       <c r="Q60" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="R60" s="9" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="S60" s="9"/>
     </row>
@@ -5691,16 +5772,16 @@
         <v>20</v>
       </c>
       <c r="C61" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="D61" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="E61" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="D61" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="E61" s="5" t="s">
-        <v>195</v>
-      </c>
       <c r="F61" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G61" s="5">
         <v>7.5</v>
@@ -5738,23 +5819,23 @@
         <v>2</v>
       </c>
       <c r="Q61" s="9" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="R61" s="9"/>
       <c r="S61" s="9"/>
     </row>
     <row r="62" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C62" s="25" t="s">
+        <v>292</v>
+      </c>
+      <c r="D62" s="5" t="s">
+        <v>293</v>
+      </c>
+      <c r="E62" s="25" t="s">
+        <v>294</v>
+      </c>
+      <c r="F62" s="25" t="s">
         <v>295</v>
-      </c>
-      <c r="D62" s="5" t="s">
-        <v>296</v>
-      </c>
-      <c r="E62" s="25" t="s">
-        <v>297</v>
-      </c>
-      <c r="F62" s="25" t="s">
-        <v>298</v>
       </c>
       <c r="G62" s="5">
         <v>7</v>
@@ -5792,10 +5873,10 @@
         <v>4</v>
       </c>
       <c r="Q62" s="23" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="R62" s="23" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="S62" s="9"/>
       <c r="U62" s="24"/>
@@ -5808,16 +5889,16 @@
         <v>20</v>
       </c>
       <c r="C63" s="12" t="s">
+        <v>195</v>
+      </c>
+      <c r="D63" s="21" t="s">
+        <v>196</v>
+      </c>
+      <c r="E63" s="12" t="s">
         <v>197</v>
       </c>
-      <c r="D63" s="21" t="s">
-        <v>198</v>
-      </c>
-      <c r="E63" s="12" t="s">
-        <v>199</v>
-      </c>
       <c r="F63" s="12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G63" s="12">
         <v>7</v>
@@ -5855,13 +5936,13 @@
         <v>3</v>
       </c>
       <c r="Q63" s="9" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="R63" s="23" t="s">
+        <v>367</v>
+      </c>
+      <c r="S63" s="23" t="s">
         <v>371</v>
-      </c>
-      <c r="S63" s="23" t="s">
-        <v>375</v>
       </c>
       <c r="U63" s="24"/>
     </row>
@@ -5873,16 +5954,16 @@
         <v>30</v>
       </c>
       <c r="C64" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="D64" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="E64" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="D64" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="E64" s="5" t="s">
-        <v>202</v>
-      </c>
       <c r="F64" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G64" s="5">
         <v>8</v>
@@ -5920,23 +6001,23 @@
         <v>3</v>
       </c>
       <c r="Q64" s="24" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="R64" s="9"/>
       <c r="S64" s="9"/>
     </row>
     <row r="65" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C65" s="5" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D65" s="5" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E65" s="5" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="F65" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G65" s="5">
         <v>9</v>
@@ -5974,23 +6055,23 @@
         <v>4</v>
       </c>
       <c r="Q65" s="23" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="R65" s="9"/>
       <c r="S65" s="9"/>
     </row>
     <row r="66" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C66" s="5" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D66" s="5" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G66" s="5">
         <v>9.6</v>
@@ -6028,23 +6109,23 @@
         <v>4</v>
       </c>
       <c r="Q66" s="9" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="R66" s="9"/>
       <c r="S66" s="9"/>
     </row>
     <row r="67" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C67" s="5" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D67" s="5" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F67" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G67" s="5">
         <v>8</v>
@@ -6082,10 +6163,10 @@
         <v>4</v>
       </c>
       <c r="Q67" s="9" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="R67" s="23" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="S67" s="9"/>
       <c r="U67" s="24"/>
@@ -6098,16 +6179,16 @@
         <v>40</v>
       </c>
       <c r="C68" s="12" t="s">
+        <v>209</v>
+      </c>
+      <c r="D68" s="12" t="s">
+        <v>210</v>
+      </c>
+      <c r="E68" s="12" t="s">
         <v>211</v>
       </c>
-      <c r="D68" s="12" t="s">
-        <v>212</v>
-      </c>
-      <c r="E68" s="12" t="s">
-        <v>213</v>
-      </c>
       <c r="F68" s="12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G68" s="12">
         <v>9</v>
@@ -6145,23 +6226,23 @@
         <v>5</v>
       </c>
       <c r="Q68" s="9" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="R68" s="9"/>
       <c r="S68" s="9"/>
     </row>
     <row r="69" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C69" s="12" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D69" s="12" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="E69" s="12" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="F69" s="12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G69" s="12">
         <v>10</v>
@@ -6199,7 +6280,7 @@
         <v>4</v>
       </c>
       <c r="Q69" s="23" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="R69" s="9"/>
       <c r="S69" s="9"/>
@@ -6212,16 +6293,16 @@
         <v>45</v>
       </c>
       <c r="C70" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="D70" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="E70" s="5" t="s">
         <v>222</v>
       </c>
-      <c r="D70" s="5" t="s">
-        <v>223</v>
-      </c>
-      <c r="E70" s="5" t="s">
-        <v>224</v>
-      </c>
       <c r="F70" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G70" s="5">
         <v>14</v>
@@ -6259,25 +6340,25 @@
         <v>5</v>
       </c>
       <c r="Q70" s="9" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="R70" s="9" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="S70" s="9"/>
     </row>
     <row r="71" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C71" s="5" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="E71" s="25" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="F71" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G71" s="5">
         <v>14</v>
@@ -6315,28 +6396,28 @@
         <v>6</v>
       </c>
       <c r="Q71" s="23" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="R71" s="23" t="s">
+        <v>325</v>
+      </c>
+      <c r="S71" s="23" t="s">
         <v>329</v>
-      </c>
-      <c r="S71" s="23" t="s">
-        <v>333</v>
       </c>
       <c r="U71" s="24"/>
     </row>
     <row r="72" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C72" s="5" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D72" s="5" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="F72" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G72" s="5">
         <v>15</v>
@@ -6373,17 +6454,17 @@
       <c r="P72" s="9">
         <v>5</v>
       </c>
-      <c r="Q72" s="9" t="s">
-        <v>181</v>
+      <c r="Q72" s="23" t="s">
+        <v>436</v>
       </c>
       <c r="R72" s="9" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="S72" s="9" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="T72" s="24" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="U72" s="24"/>
     </row>
@@ -6395,16 +6476,16 @@
         <v>45</v>
       </c>
       <c r="C73" s="12" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="D73" s="12" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="E73" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F73" s="12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G73" s="12">
         <v>14</v>
@@ -6442,26 +6523,26 @@
         <v>5</v>
       </c>
       <c r="Q73" s="23" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="R73" s="23" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="S73" s="9"/>
       <c r="U73" s="24"/>
     </row>
     <row r="74" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C74" s="12" t="s">
+        <v>226</v>
+      </c>
+      <c r="D74" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="E74" s="12" t="s">
         <v>228</v>
       </c>
-      <c r="D74" s="12" t="s">
-        <v>229</v>
-      </c>
-      <c r="E74" s="12" t="s">
-        <v>230</v>
-      </c>
       <c r="F74" s="12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G74" s="12">
         <v>14</v>
@@ -6499,25 +6580,25 @@
         <v>7</v>
       </c>
       <c r="Q74" s="23" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="R74" s="23" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="S74" s="9"/>
     </row>
     <row r="75" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C75" s="12" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="D75" s="12" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="E75" s="12" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="F75" s="12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G75" s="12">
         <v>13</v>
@@ -6533,7 +6614,7 @@
         <v>29.5</v>
       </c>
       <c r="K75" s="9">
-        <f t="shared" ref="K75:K107" si="41">(G75*$I$4)+(H75*$I$5)+(I75*$I$7)</f>
+        <f t="shared" ref="K75:K109" si="41">(G75*$I$4)+(H75*$I$5)+(I75*$I$7)</f>
         <v>10</v>
       </c>
       <c r="L75" s="10">
@@ -6555,26 +6636,26 @@
         <v>5</v>
       </c>
       <c r="Q75" s="9" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="R75" s="23" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="S75" s="9"/>
       <c r="U75" s="24"/>
     </row>
     <row r="76" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C76" s="12" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="D76" s="12" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="E76" s="12" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="F76" s="12" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="G76" s="12">
         <v>9.5</v>
@@ -6612,10 +6693,10 @@
         <v>5</v>
       </c>
       <c r="Q76" s="23" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="R76" s="23" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="S76" s="9"/>
       <c r="U76" s="24"/>
@@ -6628,16 +6709,16 @@
         <v>60</v>
       </c>
       <c r="C77" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="D77" s="29" t="s">
+        <v>373</v>
+      </c>
+      <c r="E77" s="5" t="s">
         <v>231</v>
       </c>
-      <c r="D77" s="29" t="s">
-        <v>377</v>
-      </c>
-      <c r="E77" s="5" t="s">
-        <v>233</v>
-      </c>
       <c r="F77" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G77" s="5">
         <v>15</v>
@@ -6675,7 +6756,7 @@
         <v>7</v>
       </c>
       <c r="Q77" s="23" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="R77" s="9"/>
       <c r="S77" s="9"/>
@@ -6683,16 +6764,16 @@
     </row>
     <row r="78" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C78" s="5" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="D78" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="E78" s="5" t="s">
         <v>232</v>
       </c>
-      <c r="E78" s="5" t="s">
-        <v>234</v>
-      </c>
       <c r="F78" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G78" s="5">
         <v>16</v>
@@ -6730,25 +6811,25 @@
         <v>7</v>
       </c>
       <c r="Q78" s="23" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="R78" s="23" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="S78" s="9"/>
     </row>
     <row r="79" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C79" s="5" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="D79" s="5" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="F79" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G79" s="5">
         <v>19</v>
@@ -6786,7 +6867,7 @@
         <v>6</v>
       </c>
       <c r="Q79" s="23" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="R79" s="23"/>
       <c r="S79" s="9"/>
@@ -6794,16 +6875,16 @@
     </row>
     <row r="80" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C80" s="5" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="D80" s="5" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E80" s="5" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="F80" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G80" s="5">
         <v>13</v>
@@ -6841,7 +6922,7 @@
         <v>10</v>
       </c>
       <c r="Q80" s="23" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="R80" s="9"/>
       <c r="S80" s="9"/>
@@ -6849,16 +6930,16 @@
     </row>
     <row r="81" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C81" s="5" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="D81" s="5" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="E81" s="5" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="F81" s="5" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="G81" s="5">
         <v>18</v>
@@ -6896,10 +6977,10 @@
         <v>6</v>
       </c>
       <c r="Q81" s="9" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="R81" s="9" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="S81" s="9"/>
       <c r="U81" s="24"/>
@@ -6912,16 +6993,16 @@
         <v>65</v>
       </c>
       <c r="C82" s="12" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="D82" s="12" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="E82" s="12" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="F82" s="12" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="G82" s="12">
         <v>20</v>
@@ -6959,25 +7040,25 @@
         <v>8</v>
       </c>
       <c r="Q82" s="9" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="R82" s="9" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="S82" s="9"/>
     </row>
     <row r="83" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C83" s="12" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="D83" s="12" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="E83" s="12" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="F83" s="12" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="G83" s="12">
         <v>23</v>
@@ -7015,25 +7096,25 @@
         <v>8</v>
       </c>
       <c r="Q83" s="23" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="R83" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="S83" s="9"/>
     </row>
     <row r="84" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C84" s="12" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="D84" s="12" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="E84" s="12" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="F84" s="12" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="G84" s="12">
         <v>17</v>
@@ -7071,25 +7152,25 @@
         <v>8</v>
       </c>
       <c r="Q84" s="23" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="R84" s="23" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="S84" s="9"/>
     </row>
     <row r="85" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C85" s="12" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="D85" s="12" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="E85" s="12" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="F85" s="12" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="G85" s="12">
         <v>15</v>
@@ -7127,26 +7208,26 @@
         <v>8</v>
       </c>
       <c r="Q85" s="23" t="s">
-        <v>307</v>
+        <v>436</v>
       </c>
       <c r="R85" s="23" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="S85" s="9"/>
       <c r="U85" s="24"/>
     </row>
     <row r="86" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C86" s="12" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="D86" s="12" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="E86" s="12" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="F86" s="12" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="G86" s="12">
         <v>10</v>
@@ -7184,26 +7265,26 @@
         <v>6</v>
       </c>
       <c r="Q86" s="23" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="R86" s="23" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="S86" s="9"/>
       <c r="U86" s="24"/>
     </row>
     <row r="87" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C87" s="12" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="D87" s="12" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="E87" s="12" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="F87" s="12" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="G87" s="12">
         <v>19</v>
@@ -7241,28 +7322,28 @@
         <v>6</v>
       </c>
       <c r="Q87" s="23" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="R87" s="23" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="S87" s="23" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="U87" s="24"/>
     </row>
     <row r="88" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C88" s="12" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="D88" s="12" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="E88" s="12" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="F88" s="12" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="G88" s="12">
         <v>13</v>
@@ -7300,7 +7381,7 @@
         <v>4</v>
       </c>
       <c r="Q88" s="23" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="R88" s="23"/>
       <c r="S88" s="23"/>
@@ -7314,16 +7395,16 @@
         <v>70</v>
       </c>
       <c r="C89" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="D89" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="E89" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="D89" s="5" t="s">
-        <v>238</v>
-      </c>
-      <c r="E89" s="5" t="s">
-        <v>239</v>
-      </c>
       <c r="F89" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G89" s="5">
         <v>25</v>
@@ -7361,31 +7442,31 @@
         <v>9</v>
       </c>
       <c r="Q89" s="23" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="R89" s="23" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="S89" s="9" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="T89" s="24" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="U89" s="24"/>
     </row>
     <row r="90" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C90" s="5" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="D90" s="5" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="F90" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G90" s="5">
         <v>19</v>
@@ -7423,28 +7504,28 @@
         <v>6</v>
       </c>
       <c r="Q90" s="23" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="R90" s="23" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="S90" s="23" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="U90" s="24"/>
     </row>
     <row r="91" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C91" s="5" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="D91" s="5" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="E91" s="5" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="F91" s="5" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="G91" s="5">
         <v>21</v>
@@ -7482,10 +7563,10 @@
         <v>8</v>
       </c>
       <c r="Q91" s="23" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="R91" s="23" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="S91" s="23"/>
       <c r="U91" s="24"/>
@@ -7498,16 +7579,16 @@
         <v>75</v>
       </c>
       <c r="C92" s="12" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="D92" s="12" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="E92" s="26" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="F92" s="12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G92" s="12">
         <v>26</v>
@@ -7545,28 +7626,28 @@
         <v>9</v>
       </c>
       <c r="Q92" s="9" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="R92" s="23" t="s">
-        <v>287</v>
+        <v>437</v>
       </c>
       <c r="S92" s="23" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="U92" s="24"/>
     </row>
     <row r="93" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C93" s="12" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="D93" s="12" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E93" s="12" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="F93" s="12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G93" s="12">
         <v>22</v>
@@ -7604,28 +7685,28 @@
         <v>6</v>
       </c>
       <c r="Q93" s="23" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="R93" s="23" t="s">
-        <v>307</v>
+        <v>436</v>
       </c>
       <c r="S93" s="23" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="U93" s="24"/>
     </row>
     <row r="94" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C94" s="12" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="D94" s="12" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="E94" s="12" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="F94" s="12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G94" s="12">
         <v>18</v>
@@ -7663,13 +7744,13 @@
         <v>8</v>
       </c>
       <c r="Q94" s="23" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="R94" s="23" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="S94" s="23" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="U94" s="24"/>
     </row>
@@ -7681,16 +7762,16 @@
         <v>65</v>
       </c>
       <c r="C95" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="D95" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="E95" s="5" t="s">
         <v>247</v>
       </c>
-      <c r="D95" s="5" t="s">
-        <v>248</v>
-      </c>
-      <c r="E95" s="5" t="s">
-        <v>249</v>
-      </c>
       <c r="F95" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G95" s="5">
         <v>14</v>
@@ -7702,7 +7783,7 @@
         <v>10</v>
       </c>
       <c r="J95" s="17">
-        <f t="shared" ref="J95:J104" si="49">(G95*$I$2)+(H95*$I$3)</f>
+        <f t="shared" ref="J95:J106" si="49">(G95*$I$2)+(H95*$I$3)</f>
         <v>40.5</v>
       </c>
       <c r="K95" s="9">
@@ -7710,15 +7791,15 @@
         <v>19.5</v>
       </c>
       <c r="L95" s="10">
-        <f t="shared" ref="L95:L104" si="50">J95+K95</f>
+        <f t="shared" ref="L95:L106" si="50">J95+K95</f>
         <v>60</v>
       </c>
       <c r="M95" s="11">
-        <f t="shared" ref="M95:M118" si="51">I95*$M$2</f>
+        <f t="shared" ref="M95:M121" si="51">I95*$M$2</f>
         <v>62.5</v>
       </c>
       <c r="N95" s="11">
-        <f t="shared" ref="N95:N118" si="52">I95*$M$3</f>
+        <f t="shared" ref="N95:N121" si="52">I95*$M$3</f>
         <v>15</v>
       </c>
       <c r="O95" s="9">
@@ -7728,13 +7809,13 @@
         <v>9</v>
       </c>
       <c r="Q95" s="23" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="R95" s="23" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="S95" s="23" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="U95" s="24"/>
     </row>
@@ -7746,16 +7827,16 @@
         <v>80</v>
       </c>
       <c r="C96" s="12" t="s">
+        <v>250</v>
+      </c>
+      <c r="D96" s="12" t="s">
+        <v>251</v>
+      </c>
+      <c r="E96" s="12" t="s">
         <v>252</v>
       </c>
-      <c r="D96" s="12" t="s">
-        <v>253</v>
-      </c>
-      <c r="E96" s="12" t="s">
-        <v>254</v>
-      </c>
       <c r="F96" s="12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G96" s="12">
         <v>25</v>
@@ -7793,31 +7874,31 @@
         <v>10</v>
       </c>
       <c r="Q96" s="3" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="R96" s="23" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="S96" s="9" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="T96" s="24" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="U96" s="24"/>
     </row>
     <row r="97" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C97" s="12" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="D97" s="12" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="E97" s="12" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="F97" s="12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G97" s="12">
         <v>25</v>
@@ -7855,13 +7936,13 @@
         <v>12</v>
       </c>
       <c r="Q97" s="9" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="R97" s="23" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="S97" s="23" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="U97" s="24"/>
     </row>
@@ -7873,7 +7954,7 @@
         <v>85</v>
       </c>
       <c r="C98" s="9" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D98" s="9"/>
       <c r="E98" s="9"/>
@@ -7943,20 +8024,20 @@
     </row>
     <row r="100" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="24" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="B100" s="24" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="C100" s="9" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="D100" s="23"/>
       <c r="E100" s="23" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="F100" s="23" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="G100" s="9">
         <v>28</v>
@@ -7994,14 +8075,14 @@
         <v>6</v>
       </c>
       <c r="Q100" s="23" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="R100" s="23" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="S100" s="23"/>
       <c r="T100" s="23" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
     </row>
     <row r="101" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
@@ -8012,14 +8093,14 @@
         <v>125</v>
       </c>
       <c r="C101" s="9" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="D101" s="23"/>
       <c r="E101" s="23" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="F101" s="23" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="G101" s="9">
         <v>32</v>
@@ -8057,26 +8138,26 @@
         <v>8</v>
       </c>
       <c r="Q101" s="23" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="R101" s="23" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="S101" s="23"/>
       <c r="T101" s="23" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
     </row>
     <row r="102" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C102" s="9" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="D102" s="23"/>
       <c r="E102" s="23" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="F102" s="23" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="G102" s="9">
         <v>30</v>
@@ -8088,7 +8169,7 @@
         <v>20</v>
       </c>
       <c r="J102" s="17">
-        <f t="shared" ref="J102" si="53">(G102*$I$2)+(H102*$I$3)</f>
+        <f t="shared" ref="J102:J103" si="53">(G102*$I$2)+(H102*$I$3)</f>
         <v>75</v>
       </c>
       <c r="K102" s="9">
@@ -8114,376 +8195,401 @@
         <v>9</v>
       </c>
       <c r="Q102" s="23" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="R102" s="23" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="S102" s="23"/>
       <c r="T102" s="23" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="103" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A103" s="3">
+      <c r="C103" s="9" t="s">
+        <v>382</v>
+      </c>
+      <c r="D103" s="23"/>
+      <c r="E103" s="9" t="s">
+        <v>423</v>
+      </c>
+      <c r="F103" s="23" t="s">
+        <v>295</v>
+      </c>
+      <c r="G103" s="9">
+        <v>30</v>
+      </c>
+      <c r="H103" s="9">
+        <v>32</v>
+      </c>
+      <c r="I103" s="9">
+        <v>19</v>
+      </c>
+      <c r="J103" s="17">
+        <f t="shared" ref="J103:J104" si="58">(G103*$I$2)+(H103*$I$3)</f>
+        <v>76</v>
+      </c>
+      <c r="K103" s="9">
+        <f t="shared" ref="K103:K104" si="59">(G103*$I$4)+(H103*$I$5)+(I103*$I$7)</f>
+        <v>31</v>
+      </c>
+      <c r="L103" s="10">
+        <f t="shared" ref="L103:L104" si="60">J103+K103</f>
+        <v>107</v>
+      </c>
+      <c r="M103" s="11">
+        <f t="shared" ref="M103:M104" si="61">I103*$M$2</f>
+        <v>118.75</v>
+      </c>
+      <c r="N103" s="11">
+        <f t="shared" ref="N103:N104" si="62">I103*$M$3</f>
+        <v>28.5</v>
+      </c>
+      <c r="O103" s="9">
+        <v>4</v>
+      </c>
+      <c r="P103" s="9">
+        <v>7</v>
+      </c>
+      <c r="Q103" s="23" t="s">
+        <v>429</v>
+      </c>
+      <c r="R103" s="23" t="s">
+        <v>325</v>
+      </c>
+      <c r="S103" s="23"/>
+      <c r="T103" s="23"/>
+    </row>
+    <row r="104" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C104" s="9" t="s">
+        <v>382</v>
+      </c>
+      <c r="D104" s="23"/>
+      <c r="E104" s="23" t="s">
+        <v>424</v>
+      </c>
+      <c r="F104" s="23" t="s">
+        <v>318</v>
+      </c>
+      <c r="G104" s="9">
+        <v>26</v>
+      </c>
+      <c r="H104" s="9">
+        <v>35</v>
+      </c>
+      <c r="I104" s="9">
+        <v>20</v>
+      </c>
+      <c r="J104" s="17">
+        <f t="shared" si="58"/>
+        <v>69.5</v>
+      </c>
+      <c r="K104" s="9">
+        <f t="shared" si="59"/>
+        <v>30.5</v>
+      </c>
+      <c r="L104" s="10">
+        <f t="shared" si="60"/>
+        <v>100</v>
+      </c>
+      <c r="M104" s="11">
+        <f t="shared" si="61"/>
+        <v>125</v>
+      </c>
+      <c r="N104" s="11">
+        <f t="shared" si="62"/>
+        <v>30</v>
+      </c>
+      <c r="O104" s="9">
+        <v>4</v>
+      </c>
+      <c r="P104" s="9">
+        <v>7</v>
+      </c>
+      <c r="Q104" s="23" t="s">
+        <v>431</v>
+      </c>
+      <c r="R104" s="23" t="s">
+        <v>432</v>
+      </c>
+      <c r="S104" s="23" t="s">
+        <v>419</v>
+      </c>
+      <c r="T104" s="23"/>
+    </row>
+    <row r="105" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A105" s="3">
         <v>120</v>
       </c>
-      <c r="B103" s="3">
+      <c r="B105" s="3">
         <v>140</v>
       </c>
-      <c r="C103" s="9" t="s">
-        <v>387</v>
-      </c>
-      <c r="D103" s="23"/>
-      <c r="E103" s="23" t="s">
-        <v>395</v>
-      </c>
-      <c r="F103" s="23" t="s">
-        <v>298</v>
-      </c>
-      <c r="G103" s="9">
+      <c r="C105" s="9" t="s">
+        <v>383</v>
+      </c>
+      <c r="D105" s="23"/>
+      <c r="E105" s="23" t="s">
+        <v>391</v>
+      </c>
+      <c r="F105" s="23" t="s">
+        <v>295</v>
+      </c>
+      <c r="G105" s="9">
         <v>36</v>
       </c>
-      <c r="H103" s="9">
+      <c r="H105" s="9">
         <v>30</v>
       </c>
-      <c r="I103" s="9">
+      <c r="I105" s="9">
         <v>22.5</v>
       </c>
-      <c r="J103" s="17">
+      <c r="J105" s="17">
         <f t="shared" si="49"/>
         <v>87</v>
       </c>
-      <c r="K103" s="9">
+      <c r="K105" s="9">
         <f t="shared" si="41"/>
         <v>33</v>
       </c>
-      <c r="L103" s="10">
+      <c r="L105" s="10">
         <f t="shared" si="50"/>
         <v>120</v>
       </c>
-      <c r="M103" s="11">
+      <c r="M105" s="11">
         <f t="shared" si="51"/>
         <v>140.625</v>
       </c>
-      <c r="N103" s="11">
+      <c r="N105" s="11">
         <f t="shared" si="52"/>
         <v>33.75</v>
       </c>
-      <c r="O103" s="9">
+      <c r="O105" s="9">
         <v>6</v>
       </c>
-      <c r="P103" s="9">
+      <c r="P105" s="9">
         <v>9</v>
       </c>
-      <c r="Q103" s="23" t="s">
-        <v>405</v>
-      </c>
-      <c r="R103" s="23" t="s">
-        <v>406</v>
-      </c>
-      <c r="S103" s="23"/>
-      <c r="T103" s="23" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="104" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C104" s="9" t="s">
-        <v>387</v>
-      </c>
-      <c r="D104" s="23"/>
-      <c r="E104" s="23" t="s">
-        <v>397</v>
-      </c>
-      <c r="F104" s="23" t="s">
-        <v>322</v>
-      </c>
-      <c r="G104" s="9">
+      <c r="Q105" s="23" t="s">
+        <v>401</v>
+      </c>
+      <c r="R105" s="23" t="s">
+        <v>402</v>
+      </c>
+      <c r="S105" s="23"/>
+      <c r="T105" s="23" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="106" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C106" s="9" t="s">
+        <v>383</v>
+      </c>
+      <c r="D106" s="23"/>
+      <c r="E106" s="23" t="s">
+        <v>393</v>
+      </c>
+      <c r="F106" s="23" t="s">
+        <v>318</v>
+      </c>
+      <c r="G106" s="9">
         <v>35</v>
       </c>
-      <c r="H104" s="9">
+      <c r="H106" s="9">
         <v>26</v>
       </c>
-      <c r="I104" s="9">
+      <c r="I106" s="9">
         <v>22</v>
       </c>
-      <c r="J104" s="17">
+      <c r="J106" s="17">
         <f t="shared" si="49"/>
         <v>83</v>
       </c>
-      <c r="K104" s="9">
+      <c r="K106" s="9">
         <f t="shared" si="41"/>
         <v>30.5</v>
       </c>
-      <c r="L104" s="10">
+      <c r="L106" s="10">
         <f t="shared" si="50"/>
         <v>113.5</v>
       </c>
-      <c r="M104" s="11">
+      <c r="M106" s="11">
         <f t="shared" si="51"/>
         <v>137.5</v>
       </c>
-      <c r="N104" s="11">
+      <c r="N106" s="11">
         <f t="shared" si="52"/>
         <v>33</v>
       </c>
-      <c r="O104" s="9">
+      <c r="O106" s="9">
         <v>6</v>
       </c>
-      <c r="P104" s="9">
+      <c r="P106" s="9">
         <v>10</v>
       </c>
-      <c r="Q104" s="23" t="s">
-        <v>425</v>
-      </c>
-      <c r="R104" s="23" t="s">
+      <c r="Q106" s="23" t="s">
+        <v>420</v>
+      </c>
+      <c r="R106" s="23" t="s">
+        <v>410</v>
+      </c>
+      <c r="S106" s="23" t="s">
+        <v>421</v>
+      </c>
+      <c r="T106" s="24"/>
+    </row>
+    <row r="107" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C107" s="23" t="s">
+        <v>405</v>
+      </c>
+      <c r="D107" s="23"/>
+      <c r="E107" s="23" t="s">
+        <v>406</v>
+      </c>
+      <c r="F107" s="23" t="s">
+        <v>295</v>
+      </c>
+      <c r="G107" s="9">
+        <v>38</v>
+      </c>
+      <c r="H107" s="9">
+        <v>24</v>
+      </c>
+      <c r="I107" s="9">
+        <v>23</v>
+      </c>
+      <c r="J107" s="17">
+        <f t="shared" ref="J107" si="63">(G107*$I$2)+(H107*$I$3)</f>
+        <v>88</v>
+      </c>
+      <c r="K107" s="9">
+        <f t="shared" ref="K107" si="64">(G107*$I$4)+(H107*$I$5)+(I107*$I$7)</f>
+        <v>31</v>
+      </c>
+      <c r="L107" s="10">
+        <f t="shared" ref="L107" si="65">J107+K107</f>
+        <v>119</v>
+      </c>
+      <c r="M107" s="11">
+        <f t="shared" ref="M107" si="66">I107*$M$2</f>
+        <v>143.75</v>
+      </c>
+      <c r="N107" s="11">
+        <f t="shared" ref="N107" si="67">I107*$M$3</f>
+        <v>34.5</v>
+      </c>
+      <c r="O107" s="9">
+        <v>7</v>
+      </c>
+      <c r="P107" s="9">
+        <v>13</v>
+      </c>
+      <c r="Q107" s="23" t="s">
+        <v>430</v>
+      </c>
+      <c r="R107" s="23" t="s">
+        <v>438</v>
+      </c>
+      <c r="S107" s="23" t="s">
+        <v>408</v>
+      </c>
+      <c r="T107" s="24" t="s">
+        <v>407</v>
+      </c>
+      <c r="U107" s="24" t="s">
         <v>415</v>
       </c>
-      <c r="S104" s="23" t="s">
-        <v>426</v>
-      </c>
-      <c r="T104" s="24"/>
-    </row>
-    <row r="105" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C105" s="23" t="s">
-        <v>409</v>
-      </c>
-      <c r="D105" s="23"/>
-      <c r="E105" s="23" t="s">
-        <v>410</v>
-      </c>
-      <c r="F105" s="23" t="s">
-        <v>298</v>
-      </c>
-      <c r="G105" s="9">
-        <v>38</v>
-      </c>
-      <c r="H105" s="9">
-        <v>24</v>
-      </c>
-      <c r="I105" s="9">
-        <v>22</v>
-      </c>
-      <c r="J105" s="17">
-        <f t="shared" ref="J105" si="58">(G105*$I$2)+(H105*$I$3)</f>
-        <v>88</v>
-      </c>
-      <c r="K105" s="9">
-        <f t="shared" ref="K105" si="59">(G105*$I$4)+(H105*$I$5)+(I105*$I$7)</f>
-        <v>31</v>
-      </c>
-      <c r="L105" s="10">
-        <f t="shared" ref="L105" si="60">J105+K105</f>
-        <v>119</v>
-      </c>
-      <c r="M105" s="11">
-        <f t="shared" ref="M105" si="61">I105*$M$2</f>
-        <v>137.5</v>
-      </c>
-      <c r="N105" s="11">
-        <f t="shared" ref="N105" si="62">I105*$M$3</f>
-        <v>33</v>
-      </c>
-      <c r="O105" s="9">
-        <v>7</v>
-      </c>
-      <c r="P105" s="9">
-        <v>13</v>
-      </c>
-      <c r="Q105" s="23" t="s">
-        <v>411</v>
-      </c>
-      <c r="R105" s="23" t="s">
-        <v>424</v>
-      </c>
-      <c r="S105" s="23" t="s">
-        <v>413</v>
-      </c>
-      <c r="T105" s="24" t="s">
-        <v>412</v>
-      </c>
-      <c r="U105" s="24" t="s">
-        <v>420</v>
-      </c>
-      <c r="V105" s="24" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="106" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A106" s="3">
-        <v>135</v>
-      </c>
-      <c r="B106" s="3">
-        <v>155</v>
-      </c>
-      <c r="C106" s="9" t="s">
-        <v>384</v>
-      </c>
-      <c r="D106" s="9"/>
-      <c r="E106" s="9"/>
-      <c r="F106" s="9"/>
-      <c r="G106" s="9"/>
-      <c r="H106" s="9"/>
-      <c r="I106" s="9"/>
-      <c r="J106" s="17">
-        <f t="shared" ref="J106:J126" si="63">(G106*$I$2)+(H106*$I$3)</f>
-        <v>0</v>
-      </c>
-      <c r="K106" s="9">
-        <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-      <c r="L106" s="10">
-        <f t="shared" ref="L106:L126" si="64">J106+K106</f>
-        <v>0</v>
-      </c>
-      <c r="M106" s="11">
-        <f t="shared" si="51"/>
-        <v>0</v>
-      </c>
-      <c r="N106" s="11">
-        <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
-      <c r="O106" s="9"/>
-      <c r="P106" s="9"/>
-      <c r="Q106" s="9"/>
-      <c r="R106" s="9"/>
-      <c r="S106" s="9"/>
-    </row>
-    <row r="107" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A107" s="3">
-        <v>150</v>
-      </c>
-      <c r="B107" s="3">
-        <v>165</v>
-      </c>
-      <c r="C107" s="9" t="s">
-        <v>388</v>
-      </c>
-      <c r="D107" s="9"/>
-      <c r="E107" s="9"/>
-      <c r="F107" s="9"/>
-      <c r="G107" s="9"/>
-      <c r="H107" s="9"/>
-      <c r="I107" s="9"/>
-      <c r="J107" s="17">
-        <f t="shared" si="63"/>
-        <v>0</v>
-      </c>
-      <c r="K107" s="9">
-        <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-      <c r="L107" s="10">
-        <f t="shared" si="64"/>
-        <v>0</v>
-      </c>
-      <c r="M107" s="11">
-        <f t="shared" si="51"/>
-        <v>0</v>
-      </c>
-      <c r="N107" s="11">
-        <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
-      <c r="O107" s="9"/>
-      <c r="P107" s="9"/>
-      <c r="Q107" s="9"/>
-      <c r="R107" s="9"/>
-      <c r="S107" s="9"/>
+      <c r="V107" s="24" t="s">
+        <v>418</v>
+      </c>
     </row>
     <row r="108" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="3">
-        <v>165</v>
+        <v>135</v>
       </c>
       <c r="B108" s="3">
-        <v>180</v>
-      </c>
-      <c r="C108" s="23" t="s">
-        <v>389</v>
-      </c>
-      <c r="D108" s="23"/>
+        <v>155</v>
+      </c>
+      <c r="C108" s="9" t="s">
+        <v>380</v>
+      </c>
+      <c r="D108" s="9"/>
       <c r="E108" s="23" t="s">
-        <v>394</v>
+        <v>425</v>
       </c>
       <c r="F108" s="23" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="G108" s="9">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="H108" s="9">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="I108" s="9">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="J108" s="17">
-        <f t="shared" si="63"/>
+        <f t="shared" ref="J108:J129" si="68">(G108*$I$2)+(H108*$I$3)</f>
+        <v>90</v>
+      </c>
+      <c r="K108" s="9">
+        <f t="shared" si="41"/>
+        <v>31.5</v>
+      </c>
+      <c r="L108" s="10">
+        <f t="shared" ref="L108:L129" si="69">J108+K108</f>
         <v>121.5</v>
-      </c>
-      <c r="K108" s="9">
-        <f t="shared" ref="K108:K139" si="65">(G108*$I$4)+(H108*$I$5)+(I108*$I$7)</f>
-        <v>43.5</v>
-      </c>
-      <c r="L108" s="10">
-        <f t="shared" si="64"/>
-        <v>165</v>
       </c>
       <c r="M108" s="11">
         <f t="shared" si="51"/>
-        <v>181.25</v>
+        <v>150</v>
       </c>
       <c r="N108" s="11">
         <f t="shared" si="52"/>
-        <v>43.5</v>
+        <v>36</v>
       </c>
       <c r="O108" s="9">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="P108" s="9">
-        <v>16</v>
-      </c>
-      <c r="Q108" s="23" t="s">
-        <v>427</v>
-      </c>
-      <c r="R108" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q108" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="R108" s="24" t="s">
         <v>428</v>
       </c>
-      <c r="S108" s="9" t="s">
-        <v>244</v>
-      </c>
-      <c r="T108" s="24" t="s">
-        <v>345</v>
+      <c r="S108" s="23" t="s">
+        <v>396</v>
       </c>
     </row>
     <row r="109" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="3">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="B109" s="3">
-        <v>190</v>
-      </c>
-      <c r="C109" s="23" t="s">
-        <v>390</v>
+        <v>165</v>
+      </c>
+      <c r="C109" s="9" t="s">
+        <v>384</v>
       </c>
       <c r="D109" s="9"/>
-      <c r="E109" s="9"/>
+      <c r="E109" s="23"/>
       <c r="F109" s="9"/>
       <c r="G109" s="9"/>
       <c r="H109" s="9"/>
       <c r="I109" s="9"/>
       <c r="J109" s="17">
-        <f t="shared" si="63"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="K109" s="9">
-        <f t="shared" si="65"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="L109" s="10">
-        <f t="shared" si="64"/>
+        <f t="shared" si="69"/>
         <v>0</v>
       </c>
       <c r="M109" s="11">
@@ -8501,133 +8607,181 @@
       <c r="S109" s="9"/>
     </row>
     <row r="110" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C110" s="9"/>
-      <c r="D110" s="9"/>
-      <c r="E110" s="9"/>
-      <c r="F110" s="9"/>
-      <c r="G110" s="9"/>
-      <c r="H110" s="9"/>
-      <c r="I110" s="9"/>
+      <c r="A110" s="3">
+        <v>165</v>
+      </c>
+      <c r="B110" s="3">
+        <v>180</v>
+      </c>
+      <c r="C110" s="23" t="s">
+        <v>385</v>
+      </c>
+      <c r="D110" s="23"/>
+      <c r="E110" s="23" t="s">
+        <v>390</v>
+      </c>
+      <c r="F110" s="23" t="s">
+        <v>295</v>
+      </c>
+      <c r="G110" s="9">
+        <v>52</v>
+      </c>
+      <c r="H110" s="9">
+        <v>35</v>
+      </c>
+      <c r="I110" s="9">
+        <v>29</v>
+      </c>
       <c r="J110" s="17">
-        <f t="shared" si="63"/>
-        <v>0</v>
+        <f t="shared" si="68"/>
+        <v>121.5</v>
       </c>
       <c r="K110" s="9">
-        <f t="shared" si="65"/>
-        <v>0</v>
+        <f t="shared" ref="K110:K142" si="70">(G110*$I$4)+(H110*$I$5)+(I110*$I$7)</f>
+        <v>43.5</v>
       </c>
       <c r="L110" s="10">
-        <f t="shared" si="64"/>
-        <v>0</v>
+        <f t="shared" si="69"/>
+        <v>165</v>
       </c>
       <c r="M110" s="11">
         <f t="shared" si="51"/>
-        <v>0</v>
+        <v>181.25</v>
       </c>
       <c r="N110" s="11">
         <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
-      <c r="O110" s="9"/>
-      <c r="P110" s="9"/>
-      <c r="Q110" s="9"/>
-      <c r="R110" s="9"/>
-      <c r="S110" s="9"/>
+        <v>43.5</v>
+      </c>
+      <c r="O110" s="9">
+        <v>4</v>
+      </c>
+      <c r="P110" s="9">
+        <v>16</v>
+      </c>
+      <c r="Q110" s="23" t="s">
+        <v>439</v>
+      </c>
+      <c r="R110" s="23" t="s">
+        <v>422</v>
+      </c>
+      <c r="S110" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="T110" s="24" t="s">
+        <v>341</v>
+      </c>
     </row>
     <row r="111" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A111" s="3">
-        <v>190</v>
-      </c>
-      <c r="B111" s="3">
-        <v>190</v>
-      </c>
-      <c r="C111" s="9" t="s">
+      <c r="C111" s="23" t="s">
         <v>385</v>
       </c>
-      <c r="D111" s="9"/>
-      <c r="E111" s="9"/>
-      <c r="F111" s="9"/>
-      <c r="G111" s="9"/>
-      <c r="H111" s="9"/>
-      <c r="I111" s="9"/>
+      <c r="D111" s="23"/>
+      <c r="E111" s="23" t="s">
+        <v>426</v>
+      </c>
+      <c r="F111" s="23" t="s">
+        <v>318</v>
+      </c>
+      <c r="G111" s="9">
+        <v>46</v>
+      </c>
+      <c r="H111" s="9">
+        <v>50</v>
+      </c>
+      <c r="I111" s="9">
+        <v>29</v>
+      </c>
       <c r="J111" s="17">
-        <f t="shared" si="63"/>
-        <v>0</v>
+        <f t="shared" ref="J111" si="71">(G111*$I$2)+(H111*$I$3)</f>
+        <v>117</v>
       </c>
       <c r="K111" s="9">
-        <f t="shared" si="65"/>
-        <v>0</v>
+        <f t="shared" ref="K111" si="72">(G111*$I$4)+(H111*$I$5)+(I111*$I$7)</f>
+        <v>48</v>
       </c>
       <c r="L111" s="10">
-        <f t="shared" si="64"/>
-        <v>0</v>
+        <f t="shared" ref="L111" si="73">J111+K111</f>
+        <v>165</v>
       </c>
       <c r="M111" s="11">
-        <f t="shared" si="51"/>
-        <v>0</v>
+        <f t="shared" ref="M111" si="74">I111*$M$2</f>
+        <v>181.25</v>
       </c>
       <c r="N111" s="11">
-        <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
-      <c r="O111" s="9"/>
-      <c r="P111" s="9"/>
-      <c r="Q111" s="9"/>
-      <c r="R111" s="9"/>
+        <f t="shared" ref="N111" si="75">I111*$M$3</f>
+        <v>43.5</v>
+      </c>
+      <c r="O111" s="9">
+        <v>6</v>
+      </c>
+      <c r="P111" s="9">
+        <v>8</v>
+      </c>
+      <c r="Q111" s="23" t="s">
+        <v>440</v>
+      </c>
+      <c r="R111" s="23"/>
       <c r="S111" s="9"/>
+      <c r="T111" s="24"/>
     </row>
     <row r="112" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="3">
-        <v>210</v>
+        <v>180</v>
       </c>
       <c r="B112" s="3">
-        <v>205</v>
+        <v>190</v>
       </c>
       <c r="C112" s="23" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="D112" s="9"/>
-      <c r="E112" s="9"/>
-      <c r="F112" s="9"/>
-      <c r="G112" s="9"/>
-      <c r="H112" s="9"/>
-      <c r="I112" s="9"/>
+      <c r="E112" s="23" t="s">
+        <v>427</v>
+      </c>
+      <c r="F112" s="23" t="s">
+        <v>295</v>
+      </c>
+      <c r="G112" s="9">
+        <v>52</v>
+      </c>
+      <c r="H112" s="9">
+        <v>50</v>
+      </c>
+      <c r="I112" s="9">
+        <v>30.5</v>
+      </c>
       <c r="J112" s="17">
-        <f t="shared" si="63"/>
-        <v>0</v>
+        <f t="shared" si="68"/>
+        <v>129</v>
       </c>
       <c r="K112" s="9">
-        <f t="shared" si="65"/>
-        <v>0</v>
+        <f t="shared" si="70"/>
+        <v>51</v>
       </c>
       <c r="L112" s="10">
-        <f t="shared" si="64"/>
-        <v>0</v>
+        <f t="shared" si="69"/>
+        <v>180</v>
       </c>
       <c r="M112" s="11">
         <f t="shared" si="51"/>
-        <v>0</v>
+        <v>190.625</v>
       </c>
       <c r="N112" s="11">
         <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
-      <c r="O112" s="9"/>
-      <c r="P112" s="9"/>
+        <v>45.75</v>
+      </c>
+      <c r="O112" s="9">
+        <v>6</v>
+      </c>
+      <c r="P112" s="9">
+        <v>12</v>
+      </c>
       <c r="Q112" s="9"/>
       <c r="R112" s="9"/>
       <c r="S112" s="9"/>
     </row>
     <row r="113" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A113" s="3">
-        <v>230</v>
-      </c>
-      <c r="B113" s="3">
-        <v>210</v>
-      </c>
-      <c r="C113" s="23" t="s">
-        <v>392</v>
-      </c>
+      <c r="C113" s="9"/>
       <c r="D113" s="9"/>
       <c r="E113" s="9"/>
       <c r="F113" s="9"/>
@@ -8635,15 +8789,15 @@
       <c r="H113" s="9"/>
       <c r="I113" s="9"/>
       <c r="J113" s="17">
-        <f t="shared" si="63"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="K113" s="9">
-        <f t="shared" si="65"/>
+        <f t="shared" si="70"/>
         <v>0</v>
       </c>
       <c r="L113" s="10">
-        <f t="shared" si="64"/>
+        <f t="shared" si="69"/>
         <v>0</v>
       </c>
       <c r="M113" s="11">
@@ -8662,13 +8816,13 @@
     </row>
     <row r="114" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="3">
-        <v>250</v>
+        <v>190</v>
       </c>
       <c r="B114" s="3">
-        <v>215</v>
-      </c>
-      <c r="C114" s="23" t="s">
-        <v>393</v>
+        <v>190</v>
+      </c>
+      <c r="C114" s="9" t="s">
+        <v>381</v>
       </c>
       <c r="D114" s="9"/>
       <c r="E114" s="9"/>
@@ -8677,15 +8831,15 @@
       <c r="H114" s="9"/>
       <c r="I114" s="9"/>
       <c r="J114" s="17">
-        <f t="shared" si="63"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="K114" s="9">
-        <f t="shared" si="65"/>
+        <f t="shared" si="70"/>
         <v>0</v>
       </c>
       <c r="L114" s="10">
-        <f t="shared" si="64"/>
+        <f t="shared" si="69"/>
         <v>0</v>
       </c>
       <c r="M114" s="11">
@@ -8703,7 +8857,15 @@
       <c r="S114" s="9"/>
     </row>
     <row r="115" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C115" s="9"/>
+      <c r="A115" s="3">
+        <v>210</v>
+      </c>
+      <c r="B115" s="3">
+        <v>205</v>
+      </c>
+      <c r="C115" s="23" t="s">
+        <v>387</v>
+      </c>
       <c r="D115" s="9"/>
       <c r="E115" s="9"/>
       <c r="F115" s="9"/>
@@ -8711,15 +8873,15 @@
       <c r="H115" s="9"/>
       <c r="I115" s="9"/>
       <c r="J115" s="17">
-        <f t="shared" si="63"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="K115" s="9">
-        <f t="shared" si="65"/>
+        <f t="shared" si="70"/>
         <v>0</v>
       </c>
       <c r="L115" s="10">
-        <f t="shared" si="64"/>
+        <f t="shared" si="69"/>
         <v>0</v>
       </c>
       <c r="M115" s="11">
@@ -8737,7 +8899,15 @@
       <c r="S115" s="9"/>
     </row>
     <row r="116" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C116" s="9"/>
+      <c r="A116" s="3">
+        <v>230</v>
+      </c>
+      <c r="B116" s="3">
+        <v>210</v>
+      </c>
+      <c r="C116" s="23" t="s">
+        <v>388</v>
+      </c>
       <c r="D116" s="9"/>
       <c r="E116" s="9"/>
       <c r="F116" s="9"/>
@@ -8745,15 +8915,15 @@
       <c r="H116" s="9"/>
       <c r="I116" s="9"/>
       <c r="J116" s="17">
-        <f t="shared" si="63"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="K116" s="9">
-        <f t="shared" si="65"/>
+        <f t="shared" si="70"/>
         <v>0</v>
       </c>
       <c r="L116" s="10">
-        <f t="shared" si="64"/>
+        <f t="shared" si="69"/>
         <v>0</v>
       </c>
       <c r="M116" s="11">
@@ -8771,7 +8941,15 @@
       <c r="S116" s="9"/>
     </row>
     <row r="117" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C117" s="9"/>
+      <c r="A117" s="3">
+        <v>250</v>
+      </c>
+      <c r="B117" s="3">
+        <v>215</v>
+      </c>
+      <c r="C117" s="23" t="s">
+        <v>389</v>
+      </c>
       <c r="D117" s="9"/>
       <c r="E117" s="9"/>
       <c r="F117" s="9"/>
@@ -8779,15 +8957,15 @@
       <c r="H117" s="9"/>
       <c r="I117" s="9"/>
       <c r="J117" s="17">
-        <f t="shared" si="63"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="K117" s="9">
-        <f t="shared" si="65"/>
+        <f t="shared" si="70"/>
         <v>0</v>
       </c>
       <c r="L117" s="10">
-        <f t="shared" si="64"/>
+        <f t="shared" si="69"/>
         <v>0</v>
       </c>
       <c r="M117" s="11">
@@ -8813,15 +8991,15 @@
       <c r="H118" s="9"/>
       <c r="I118" s="9"/>
       <c r="J118" s="17">
-        <f t="shared" si="63"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="K118" s="9">
-        <f t="shared" si="65"/>
+        <f t="shared" si="70"/>
         <v>0</v>
       </c>
       <c r="L118" s="10">
-        <f t="shared" si="64"/>
+        <f t="shared" si="69"/>
         <v>0</v>
       </c>
       <c r="M118" s="11">
@@ -8847,23 +9025,23 @@
       <c r="H119" s="9"/>
       <c r="I119" s="9"/>
       <c r="J119" s="17">
-        <f t="shared" si="63"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="K119" s="9">
-        <f t="shared" si="65"/>
+        <f t="shared" si="70"/>
         <v>0</v>
       </c>
       <c r="L119" s="10">
-        <f t="shared" si="64"/>
+        <f t="shared" si="69"/>
         <v>0</v>
       </c>
       <c r="M119" s="11">
-        <f t="shared" ref="M119:M162" si="66">I119*$M$2</f>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="N119" s="11">
-        <f t="shared" ref="N119:N162" si="67">I119*$M$3</f>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="O119" s="9"/>
@@ -8881,23 +9059,23 @@
       <c r="H120" s="9"/>
       <c r="I120" s="9"/>
       <c r="J120" s="17">
-        <f t="shared" si="63"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="K120" s="9">
-        <f t="shared" si="65"/>
+        <f t="shared" si="70"/>
         <v>0</v>
       </c>
       <c r="L120" s="10">
-        <f t="shared" si="64"/>
+        <f t="shared" si="69"/>
         <v>0</v>
       </c>
       <c r="M120" s="11">
-        <f t="shared" si="66"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="N120" s="11">
-        <f t="shared" si="67"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="O120" s="9"/>
@@ -8915,23 +9093,23 @@
       <c r="H121" s="9"/>
       <c r="I121" s="9"/>
       <c r="J121" s="17">
-        <f t="shared" si="63"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="K121" s="9">
-        <f t="shared" si="65"/>
+        <f t="shared" si="70"/>
         <v>0</v>
       </c>
       <c r="L121" s="10">
-        <f t="shared" si="64"/>
+        <f t="shared" si="69"/>
         <v>0</v>
       </c>
       <c r="M121" s="11">
-        <f t="shared" si="66"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="N121" s="11">
-        <f t="shared" si="67"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="O121" s="9"/>
@@ -8949,23 +9127,23 @@
       <c r="H122" s="9"/>
       <c r="I122" s="9"/>
       <c r="J122" s="17">
-        <f t="shared" si="63"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="K122" s="9">
-        <f t="shared" si="65"/>
+        <f t="shared" si="70"/>
         <v>0</v>
       </c>
       <c r="L122" s="10">
-        <f t="shared" si="64"/>
+        <f t="shared" si="69"/>
         <v>0</v>
       </c>
       <c r="M122" s="11">
-        <f t="shared" si="66"/>
+        <f t="shared" ref="M122:M165" si="76">I122*$M$2</f>
         <v>0</v>
       </c>
       <c r="N122" s="11">
-        <f t="shared" si="67"/>
+        <f t="shared" ref="N122:N165" si="77">I122*$M$3</f>
         <v>0</v>
       </c>
       <c r="O122" s="9"/>
@@ -8983,23 +9161,23 @@
       <c r="H123" s="9"/>
       <c r="I123" s="9"/>
       <c r="J123" s="17">
-        <f t="shared" si="63"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="K123" s="9">
-        <f t="shared" si="65"/>
+        <f t="shared" si="70"/>
         <v>0</v>
       </c>
       <c r="L123" s="10">
-        <f t="shared" si="64"/>
+        <f t="shared" si="69"/>
         <v>0</v>
       </c>
       <c r="M123" s="11">
-        <f t="shared" si="66"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="N123" s="11">
-        <f t="shared" si="67"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="O123" s="9"/>
@@ -9017,23 +9195,23 @@
       <c r="H124" s="9"/>
       <c r="I124" s="9"/>
       <c r="J124" s="17">
-        <f t="shared" si="63"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="K124" s="9">
-        <f t="shared" si="65"/>
+        <f t="shared" si="70"/>
         <v>0</v>
       </c>
       <c r="L124" s="10">
-        <f t="shared" si="64"/>
+        <f t="shared" si="69"/>
         <v>0</v>
       </c>
       <c r="M124" s="11">
-        <f t="shared" si="66"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="N124" s="11">
-        <f t="shared" si="67"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="O124" s="9"/>
@@ -9051,23 +9229,23 @@
       <c r="H125" s="9"/>
       <c r="I125" s="9"/>
       <c r="J125" s="17">
-        <f t="shared" si="63"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="K125" s="9">
-        <f t="shared" si="65"/>
+        <f t="shared" si="70"/>
         <v>0</v>
       </c>
       <c r="L125" s="10">
-        <f t="shared" si="64"/>
+        <f t="shared" si="69"/>
         <v>0</v>
       </c>
       <c r="M125" s="11">
-        <f t="shared" si="66"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="N125" s="11">
-        <f t="shared" si="67"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="O125" s="9"/>
@@ -9085,23 +9263,23 @@
       <c r="H126" s="9"/>
       <c r="I126" s="9"/>
       <c r="J126" s="17">
-        <f t="shared" si="63"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="K126" s="9">
-        <f t="shared" si="65"/>
+        <f t="shared" si="70"/>
         <v>0</v>
       </c>
       <c r="L126" s="10">
-        <f t="shared" si="64"/>
+        <f t="shared" si="69"/>
         <v>0</v>
       </c>
       <c r="M126" s="11">
-        <f t="shared" si="66"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="N126" s="11">
-        <f t="shared" si="67"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="O126" s="9"/>
@@ -9119,23 +9297,23 @@
       <c r="H127" s="9"/>
       <c r="I127" s="9"/>
       <c r="J127" s="17">
-        <f t="shared" ref="J127:J162" si="68">(G127*$I$2)+(H127*$I$3)</f>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="K127" s="9">
-        <f t="shared" si="65"/>
+        <f t="shared" si="70"/>
         <v>0</v>
       </c>
       <c r="L127" s="10">
-        <f t="shared" ref="L127:L162" si="69">J127+K127</f>
+        <f t="shared" si="69"/>
         <v>0</v>
       </c>
       <c r="M127" s="11">
-        <f t="shared" si="66"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="N127" s="11">
-        <f t="shared" si="67"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="O127" s="9"/>
@@ -9157,7 +9335,7 @@
         <v>0</v>
       </c>
       <c r="K128" s="9">
-        <f t="shared" si="65"/>
+        <f t="shared" si="70"/>
         <v>0</v>
       </c>
       <c r="L128" s="10">
@@ -9165,11 +9343,11 @@
         <v>0</v>
       </c>
       <c r="M128" s="11">
-        <f t="shared" si="66"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="N128" s="11">
-        <f t="shared" si="67"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="O128" s="9"/>
@@ -9191,7 +9369,7 @@
         <v>0</v>
       </c>
       <c r="K129" s="9">
-        <f t="shared" si="65"/>
+        <f t="shared" si="70"/>
         <v>0</v>
       </c>
       <c r="L129" s="10">
@@ -9199,11 +9377,11 @@
         <v>0</v>
       </c>
       <c r="M129" s="11">
-        <f t="shared" si="66"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="N129" s="11">
-        <f t="shared" si="67"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="O129" s="9"/>
@@ -9221,23 +9399,23 @@
       <c r="H130" s="9"/>
       <c r="I130" s="9"/>
       <c r="J130" s="17">
-        <f t="shared" si="68"/>
+        <f t="shared" ref="J130:J165" si="78">(G130*$I$2)+(H130*$I$3)</f>
         <v>0</v>
       </c>
       <c r="K130" s="9">
-        <f t="shared" si="65"/>
+        <f t="shared" si="70"/>
         <v>0</v>
       </c>
       <c r="L130" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" ref="L130:L165" si="79">J130+K130</f>
         <v>0</v>
       </c>
       <c r="M130" s="11">
-        <f t="shared" si="66"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="N130" s="11">
-        <f t="shared" si="67"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="O130" s="9"/>
@@ -9255,23 +9433,23 @@
       <c r="H131" s="9"/>
       <c r="I131" s="9"/>
       <c r="J131" s="17">
-        <f t="shared" si="68"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="K131" s="9">
-        <f t="shared" si="65"/>
+        <f t="shared" si="70"/>
         <v>0</v>
       </c>
       <c r="L131" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="M131" s="11">
-        <f t="shared" si="66"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="N131" s="11">
-        <f t="shared" si="67"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="O131" s="9"/>
@@ -9289,23 +9467,23 @@
       <c r="H132" s="9"/>
       <c r="I132" s="9"/>
       <c r="J132" s="17">
-        <f t="shared" si="68"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="K132" s="9">
-        <f t="shared" si="65"/>
+        <f t="shared" si="70"/>
         <v>0</v>
       </c>
       <c r="L132" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="M132" s="11">
-        <f t="shared" si="66"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="N132" s="11">
-        <f t="shared" si="67"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="O132" s="9"/>
@@ -9323,23 +9501,23 @@
       <c r="H133" s="9"/>
       <c r="I133" s="9"/>
       <c r="J133" s="17">
-        <f t="shared" si="68"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="K133" s="9">
-        <f t="shared" si="65"/>
+        <f t="shared" si="70"/>
         <v>0</v>
       </c>
       <c r="L133" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="M133" s="11">
-        <f t="shared" si="66"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="N133" s="11">
-        <f t="shared" si="67"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="O133" s="9"/>
@@ -9357,23 +9535,23 @@
       <c r="H134" s="9"/>
       <c r="I134" s="9"/>
       <c r="J134" s="17">
-        <f t="shared" si="68"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="K134" s="9">
-        <f t="shared" si="65"/>
+        <f t="shared" si="70"/>
         <v>0</v>
       </c>
       <c r="L134" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="M134" s="11">
-        <f t="shared" si="66"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="N134" s="11">
-        <f t="shared" si="67"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="O134" s="9"/>
@@ -9391,23 +9569,23 @@
       <c r="H135" s="9"/>
       <c r="I135" s="9"/>
       <c r="J135" s="17">
-        <f t="shared" si="68"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="K135" s="9">
-        <f t="shared" si="65"/>
+        <f t="shared" si="70"/>
         <v>0</v>
       </c>
       <c r="L135" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="M135" s="11">
-        <f t="shared" si="66"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="N135" s="11">
-        <f t="shared" si="67"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="O135" s="9"/>
@@ -9425,23 +9603,23 @@
       <c r="H136" s="9"/>
       <c r="I136" s="9"/>
       <c r="J136" s="17">
-        <f t="shared" si="68"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="K136" s="9">
-        <f t="shared" si="65"/>
+        <f t="shared" si="70"/>
         <v>0</v>
       </c>
       <c r="L136" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="M136" s="11">
-        <f t="shared" si="66"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="N136" s="11">
-        <f t="shared" si="67"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="O136" s="9"/>
@@ -9459,23 +9637,23 @@
       <c r="H137" s="9"/>
       <c r="I137" s="9"/>
       <c r="J137" s="17">
-        <f t="shared" si="68"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="K137" s="9">
-        <f t="shared" si="65"/>
+        <f t="shared" si="70"/>
         <v>0</v>
       </c>
       <c r="L137" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="M137" s="11">
-        <f t="shared" si="66"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="N137" s="11">
-        <f t="shared" si="67"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="O137" s="9"/>
@@ -9493,23 +9671,23 @@
       <c r="H138" s="9"/>
       <c r="I138" s="9"/>
       <c r="J138" s="17">
-        <f t="shared" si="68"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="K138" s="9">
-        <f t="shared" si="65"/>
+        <f t="shared" si="70"/>
         <v>0</v>
       </c>
       <c r="L138" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="M138" s="11">
-        <f t="shared" si="66"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="N138" s="11">
-        <f t="shared" si="67"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="O138" s="9"/>
@@ -9527,23 +9705,23 @@
       <c r="H139" s="9"/>
       <c r="I139" s="9"/>
       <c r="J139" s="17">
-        <f t="shared" si="68"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="K139" s="9">
-        <f t="shared" si="65"/>
+        <f t="shared" si="70"/>
         <v>0</v>
       </c>
       <c r="L139" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="M139" s="11">
-        <f t="shared" si="66"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="N139" s="11">
-        <f t="shared" si="67"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="O139" s="9"/>
@@ -9561,23 +9739,23 @@
       <c r="H140" s="9"/>
       <c r="I140" s="9"/>
       <c r="J140" s="17">
-        <f t="shared" si="68"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="K140" s="9">
-        <f t="shared" ref="K140:K162" si="70">(G140*$I$4)+(H140*$I$5)+(I140*$I$7)</f>
+        <f t="shared" si="70"/>
         <v>0</v>
       </c>
       <c r="L140" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="M140" s="11">
-        <f t="shared" si="66"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="N140" s="11">
-        <f t="shared" si="67"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="O140" s="9"/>
@@ -9595,7 +9773,7 @@
       <c r="H141" s="9"/>
       <c r="I141" s="9"/>
       <c r="J141" s="17">
-        <f t="shared" si="68"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="K141" s="9">
@@ -9603,15 +9781,15 @@
         <v>0</v>
       </c>
       <c r="L141" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="M141" s="11">
-        <f t="shared" si="66"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="N141" s="11">
-        <f t="shared" si="67"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="O141" s="9"/>
@@ -9629,7 +9807,7 @@
       <c r="H142" s="9"/>
       <c r="I142" s="9"/>
       <c r="J142" s="17">
-        <f t="shared" si="68"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="K142" s="9">
@@ -9637,15 +9815,15 @@
         <v>0</v>
       </c>
       <c r="L142" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="M142" s="11">
-        <f t="shared" si="66"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="N142" s="11">
-        <f t="shared" si="67"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="O142" s="9"/>
@@ -9663,23 +9841,23 @@
       <c r="H143" s="9"/>
       <c r="I143" s="9"/>
       <c r="J143" s="17">
-        <f t="shared" si="68"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="K143" s="9">
-        <f t="shared" si="70"/>
+        <f t="shared" ref="K143:K165" si="80">(G143*$I$4)+(H143*$I$5)+(I143*$I$7)</f>
         <v>0</v>
       </c>
       <c r="L143" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="M143" s="11">
-        <f t="shared" si="66"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="N143" s="11">
-        <f t="shared" si="67"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="O143" s="9"/>
@@ -9697,23 +9875,23 @@
       <c r="H144" s="9"/>
       <c r="I144" s="9"/>
       <c r="J144" s="17">
-        <f t="shared" si="68"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="K144" s="9">
-        <f t="shared" si="70"/>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="L144" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="M144" s="11">
-        <f t="shared" si="66"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="N144" s="11">
-        <f t="shared" si="67"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="O144" s="9"/>
@@ -9731,23 +9909,23 @@
       <c r="H145" s="9"/>
       <c r="I145" s="9"/>
       <c r="J145" s="17">
-        <f t="shared" si="68"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="K145" s="9">
-        <f t="shared" si="70"/>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="L145" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="M145" s="11">
-        <f t="shared" si="66"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="N145" s="11">
-        <f t="shared" si="67"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="O145" s="9"/>
@@ -9765,23 +9943,23 @@
       <c r="H146" s="9"/>
       <c r="I146" s="9"/>
       <c r="J146" s="17">
-        <f t="shared" si="68"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="K146" s="9">
-        <f t="shared" si="70"/>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="L146" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="M146" s="11">
-        <f t="shared" si="66"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="N146" s="11">
-        <f t="shared" si="67"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="O146" s="9"/>
@@ -9799,23 +9977,23 @@
       <c r="H147" s="9"/>
       <c r="I147" s="9"/>
       <c r="J147" s="17">
-        <f t="shared" si="68"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="K147" s="9">
-        <f t="shared" si="70"/>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="L147" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="M147" s="11">
-        <f t="shared" si="66"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="N147" s="11">
-        <f t="shared" si="67"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="O147" s="9"/>
@@ -9833,23 +10011,23 @@
       <c r="H148" s="9"/>
       <c r="I148" s="9"/>
       <c r="J148" s="17">
-        <f t="shared" si="68"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="K148" s="9">
-        <f t="shared" si="70"/>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="L148" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="M148" s="11">
-        <f t="shared" si="66"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="N148" s="11">
-        <f t="shared" si="67"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="O148" s="9"/>
@@ -9867,23 +10045,23 @@
       <c r="H149" s="9"/>
       <c r="I149" s="9"/>
       <c r="J149" s="17">
-        <f t="shared" si="68"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="K149" s="9">
-        <f t="shared" si="70"/>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="L149" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="M149" s="11">
-        <f t="shared" si="66"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="N149" s="11">
-        <f t="shared" si="67"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="O149" s="9"/>
@@ -9901,23 +10079,23 @@
       <c r="H150" s="9"/>
       <c r="I150" s="9"/>
       <c r="J150" s="17">
-        <f t="shared" si="68"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="K150" s="9">
-        <f t="shared" si="70"/>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="L150" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="M150" s="11">
-        <f t="shared" si="66"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="N150" s="11">
-        <f t="shared" si="67"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="O150" s="9"/>
@@ -9935,23 +10113,23 @@
       <c r="H151" s="9"/>
       <c r="I151" s="9"/>
       <c r="J151" s="17">
-        <f t="shared" si="68"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="K151" s="9">
-        <f t="shared" si="70"/>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="L151" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="M151" s="11">
-        <f t="shared" si="66"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="N151" s="11">
-        <f t="shared" si="67"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="O151" s="9"/>
@@ -9969,23 +10147,23 @@
       <c r="H152" s="9"/>
       <c r="I152" s="9"/>
       <c r="J152" s="17">
-        <f t="shared" si="68"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="K152" s="9">
-        <f t="shared" si="70"/>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="L152" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="M152" s="11">
-        <f t="shared" si="66"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="N152" s="11">
-        <f t="shared" si="67"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="O152" s="9"/>
@@ -10003,23 +10181,23 @@
       <c r="H153" s="9"/>
       <c r="I153" s="9"/>
       <c r="J153" s="17">
-        <f t="shared" si="68"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="K153" s="9">
-        <f t="shared" si="70"/>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="L153" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="M153" s="11">
-        <f t="shared" si="66"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="N153" s="11">
-        <f t="shared" si="67"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="O153" s="9"/>
@@ -10037,23 +10215,23 @@
       <c r="H154" s="9"/>
       <c r="I154" s="9"/>
       <c r="J154" s="17">
-        <f t="shared" si="68"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="K154" s="9">
-        <f t="shared" si="70"/>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="L154" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="M154" s="11">
-        <f t="shared" si="66"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="N154" s="11">
-        <f t="shared" si="67"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="O154" s="9"/>
@@ -10071,23 +10249,23 @@
       <c r="H155" s="9"/>
       <c r="I155" s="9"/>
       <c r="J155" s="17">
-        <f t="shared" si="68"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="K155" s="9">
-        <f t="shared" si="70"/>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="L155" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="M155" s="11">
-        <f t="shared" si="66"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="N155" s="11">
-        <f t="shared" si="67"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="O155" s="9"/>
@@ -10105,23 +10283,23 @@
       <c r="H156" s="9"/>
       <c r="I156" s="9"/>
       <c r="J156" s="17">
-        <f t="shared" si="68"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="K156" s="9">
-        <f t="shared" si="70"/>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="L156" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="M156" s="11">
-        <f t="shared" si="66"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="N156" s="11">
-        <f t="shared" si="67"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="O156" s="9"/>
@@ -10139,23 +10317,23 @@
       <c r="H157" s="9"/>
       <c r="I157" s="9"/>
       <c r="J157" s="17">
-        <f t="shared" si="68"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="K157" s="9">
-        <f t="shared" si="70"/>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="L157" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="M157" s="11">
-        <f t="shared" si="66"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="N157" s="11">
-        <f t="shared" si="67"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="O157" s="9"/>
@@ -10173,23 +10351,23 @@
       <c r="H158" s="9"/>
       <c r="I158" s="9"/>
       <c r="J158" s="17">
-        <f t="shared" si="68"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="K158" s="9">
-        <f t="shared" si="70"/>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="L158" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="M158" s="11">
-        <f t="shared" si="66"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="N158" s="11">
-        <f t="shared" si="67"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="O158" s="9"/>
@@ -10207,23 +10385,23 @@
       <c r="H159" s="9"/>
       <c r="I159" s="9"/>
       <c r="J159" s="17">
-        <f t="shared" si="68"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="K159" s="9">
-        <f t="shared" si="70"/>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="L159" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="M159" s="11">
-        <f t="shared" si="66"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="N159" s="11">
-        <f t="shared" si="67"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="O159" s="9"/>
@@ -10241,23 +10419,23 @@
       <c r="H160" s="9"/>
       <c r="I160" s="9"/>
       <c r="J160" s="17">
-        <f t="shared" si="68"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="K160" s="9">
-        <f t="shared" si="70"/>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="L160" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="M160" s="11">
-        <f t="shared" si="66"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="N160" s="11">
-        <f t="shared" si="67"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="O160" s="9"/>
@@ -10275,23 +10453,23 @@
       <c r="H161" s="9"/>
       <c r="I161" s="9"/>
       <c r="J161" s="17">
-        <f t="shared" si="68"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="K161" s="9">
-        <f t="shared" si="70"/>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="L161" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="M161" s="11">
-        <f t="shared" si="66"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="N161" s="11">
-        <f t="shared" si="67"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="O161" s="9"/>
@@ -10309,23 +10487,23 @@
       <c r="H162" s="9"/>
       <c r="I162" s="9"/>
       <c r="J162" s="17">
-        <f t="shared" si="68"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="K162" s="9">
-        <f t="shared" si="70"/>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="L162" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="M162" s="11">
-        <f t="shared" si="66"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="N162" s="11">
-        <f t="shared" si="67"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="O162" s="9"/>
@@ -10333,6 +10511,108 @@
       <c r="Q162" s="9"/>
       <c r="R162" s="9"/>
       <c r="S162" s="9"/>
+    </row>
+    <row r="163" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C163" s="9"/>
+      <c r="D163" s="9"/>
+      <c r="E163" s="9"/>
+      <c r="F163" s="9"/>
+      <c r="G163" s="9"/>
+      <c r="H163" s="9"/>
+      <c r="I163" s="9"/>
+      <c r="J163" s="17">
+        <f t="shared" si="78"/>
+        <v>0</v>
+      </c>
+      <c r="K163" s="9">
+        <f t="shared" si="80"/>
+        <v>0</v>
+      </c>
+      <c r="L163" s="10">
+        <f t="shared" si="79"/>
+        <v>0</v>
+      </c>
+      <c r="M163" s="11">
+        <f t="shared" si="76"/>
+        <v>0</v>
+      </c>
+      <c r="N163" s="11">
+        <f t="shared" si="77"/>
+        <v>0</v>
+      </c>
+      <c r="O163" s="9"/>
+      <c r="P163" s="9"/>
+      <c r="Q163" s="9"/>
+      <c r="R163" s="9"/>
+      <c r="S163" s="9"/>
+    </row>
+    <row r="164" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C164" s="9"/>
+      <c r="D164" s="9"/>
+      <c r="E164" s="9"/>
+      <c r="F164" s="9"/>
+      <c r="G164" s="9"/>
+      <c r="H164" s="9"/>
+      <c r="I164" s="9"/>
+      <c r="J164" s="17">
+        <f t="shared" si="78"/>
+        <v>0</v>
+      </c>
+      <c r="K164" s="9">
+        <f t="shared" si="80"/>
+        <v>0</v>
+      </c>
+      <c r="L164" s="10">
+        <f t="shared" si="79"/>
+        <v>0</v>
+      </c>
+      <c r="M164" s="11">
+        <f t="shared" si="76"/>
+        <v>0</v>
+      </c>
+      <c r="N164" s="11">
+        <f t="shared" si="77"/>
+        <v>0</v>
+      </c>
+      <c r="O164" s="9"/>
+      <c r="P164" s="9"/>
+      <c r="Q164" s="9"/>
+      <c r="R164" s="9"/>
+      <c r="S164" s="9"/>
+    </row>
+    <row r="165" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C165" s="9"/>
+      <c r="D165" s="9"/>
+      <c r="E165" s="9"/>
+      <c r="F165" s="9"/>
+      <c r="G165" s="9"/>
+      <c r="H165" s="9"/>
+      <c r="I165" s="9"/>
+      <c r="J165" s="17">
+        <f t="shared" si="78"/>
+        <v>0</v>
+      </c>
+      <c r="K165" s="9">
+        <f t="shared" si="80"/>
+        <v>0</v>
+      </c>
+      <c r="L165" s="10">
+        <f t="shared" si="79"/>
+        <v>0</v>
+      </c>
+      <c r="M165" s="11">
+        <f t="shared" si="76"/>
+        <v>0</v>
+      </c>
+      <c r="N165" s="11">
+        <f t="shared" si="77"/>
+        <v>0</v>
+      </c>
+      <c r="O165" s="9"/>
+      <c r="P165" s="9"/>
+      <c r="Q165" s="9"/>
+      <c r="R165" s="9"/>
+      <c r="S165" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -10359,45 +10639,45 @@
   <sheetData>
     <row r="1" spans="1:21" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>36</v>
-      </c>
       <c r="C1" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D1" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="E1" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="7" t="s">
-        <v>40</v>
-      </c>
       <c r="F1" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="H1" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="J1" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="J1" s="4" t="s">
-        <v>46</v>
-      </c>
       <c r="K1" s="24" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
     </row>
     <row r="2" spans="1:21" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="B2" s="25" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="C2" s="5">
         <v>7</v>
@@ -10415,10 +10695,10 @@
         <v>4</v>
       </c>
       <c r="H2" s="23" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="I2" s="23" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="J2" s="9"/>
       <c r="K2" s="9"/>
@@ -10429,10 +10709,10 @@
     </row>
     <row r="3" spans="1:21" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="B3" s="25" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="C3" s="5">
         <v>13</v>
@@ -10450,7 +10730,7 @@
         <v>5</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="I3" s="23"/>
       <c r="J3" s="9"/>
@@ -10462,10 +10742,10 @@
     </row>
     <row r="4" spans="1:21" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="B4" s="25" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="C4" s="5">
         <v>9</v>
@@ -10483,7 +10763,7 @@
         <v>5</v>
       </c>
       <c r="H4" s="23" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="I4" s="23"/>
       <c r="J4" s="9"/>
@@ -10495,10 +10775,10 @@
     </row>
     <row r="5" spans="1:21" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="12" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="B5" s="26" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="C5" s="12">
         <v>21</v>
@@ -10516,7 +10796,7 @@
         <v>6</v>
       </c>
       <c r="H5" s="23" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="I5" s="23"/>
       <c r="J5" s="9"/>
@@ -10528,10 +10808,10 @@
     </row>
     <row r="6" spans="1:21" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="B6" s="25" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="C6" s="5">
         <v>10</v>
@@ -10549,7 +10829,7 @@
         <v>6</v>
       </c>
       <c r="H6" s="23" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="I6" s="23"/>
       <c r="J6" s="9"/>
@@ -10561,10 +10841,10 @@
     </row>
     <row r="7" spans="1:21" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="12" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="B7" s="26" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="C7" s="12">
         <v>14</v>
@@ -10582,7 +10862,7 @@
         <v>4</v>
       </c>
       <c r="H7" s="23" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="I7" s="23"/>
       <c r="J7" s="23"/>
@@ -10924,45 +11204,45 @@
   <sheetData>
     <row r="5" spans="4:19" x14ac:dyDescent="0.2">
       <c r="F5" t="s">
+        <v>258</v>
+      </c>
+      <c r="G5" t="s">
+        <v>259</v>
+      </c>
+      <c r="J5" t="s">
         <v>260</v>
       </c>
-      <c r="G5" t="s">
+      <c r="M5" t="s">
         <v>261</v>
-      </c>
-      <c r="J5" t="s">
-        <v>262</v>
-      </c>
-      <c r="M5" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="6" spans="4:19" x14ac:dyDescent="0.2">
       <c r="F6" t="s">
+        <v>262</v>
+      </c>
+      <c r="G6" t="s">
+        <v>262</v>
+      </c>
+      <c r="H6" t="s">
+        <v>263</v>
+      </c>
+      <c r="I6" t="s">
         <v>264</v>
       </c>
-      <c r="G6" t="s">
+      <c r="J6" t="s">
+        <v>265</v>
+      </c>
+      <c r="K6" t="s">
+        <v>263</v>
+      </c>
+      <c r="L6" t="s">
         <v>264</v>
       </c>
-      <c r="H6" t="s">
-        <v>265</v>
-      </c>
-      <c r="I6" t="s">
-        <v>266</v>
-      </c>
-      <c r="J6" t="s">
-        <v>267</v>
-      </c>
-      <c r="K6" t="s">
-        <v>265</v>
-      </c>
-      <c r="L6" t="s">
-        <v>266</v>
-      </c>
       <c r="M6" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="N6" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="Q6" s="1">
         <v>1</v>
@@ -10970,7 +11250,7 @@
     </row>
     <row r="7" spans="4:19" x14ac:dyDescent="0.2">
       <c r="D7" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="E7" t="s">
         <v>21</v>
@@ -11057,7 +11337,7 @@
     </row>
     <row r="10" spans="4:19" x14ac:dyDescent="0.2">
       <c r="D10" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="E10" t="s">
         <v>21</v>
@@ -11148,7 +11428,7 @@
     </row>
     <row r="12" spans="4:19" x14ac:dyDescent="0.2">
       <c r="E12" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="F12">
         <v>-0.1</v>
@@ -11184,7 +11464,7 @@
     </row>
     <row r="13" spans="4:19" x14ac:dyDescent="0.2">
       <c r="E13" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="F13">
         <v>-15</v>
